--- a/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P835"/>
+  <dimension ref="A1:P842"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="84" min="1" max="1"/>
@@ -1051,7 +1051,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="28" customHeight="1" s="84">
       <c r="A6" t="inlineStr">
@@ -1119,7 +1118,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="28" customHeight="1" s="84">
       <c r="A7" t="inlineStr">
@@ -1187,7 +1185,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="28" customHeight="1" s="84">
       <c r="A8" t="inlineStr">
@@ -1255,7 +1252,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="84">
       <c r="A9" t="inlineStr">
@@ -1323,7 +1319,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10" ht="28" customHeight="1" s="84">
       <c r="A10" t="inlineStr">
@@ -1391,7 +1386,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1" s="84">
       <c r="A11" t="inlineStr">
@@ -1459,7 +1453,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1" s="84">
       <c r="A12" t="inlineStr">
@@ -1527,7 +1520,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13" ht="28" customHeight="1" s="84">
       <c r="A13" t="inlineStr">
@@ -1595,7 +1587,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14" ht="28" customHeight="1" s="84">
       <c r="A14" t="inlineStr">
@@ -1663,7 +1654,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15" ht="28" customHeight="1" s="84">
       <c r="A15" t="inlineStr">
@@ -1731,7 +1721,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="28" customHeight="1" s="84">
       <c r="A16" t="inlineStr">
@@ -1799,7 +1788,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17" ht="28" customHeight="1" s="84">
       <c r="A17" t="inlineStr">
@@ -1867,7 +1855,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18" ht="28" customHeight="1" s="84">
       <c r="A18" t="inlineStr">
@@ -1935,7 +1922,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="28" customHeight="1" s="84">
       <c r="A19" t="inlineStr">
@@ -2003,7 +1989,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="28" customHeight="1" s="84">
       <c r="A20" t="inlineStr">
@@ -2071,7 +2056,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21" ht="28" customHeight="1" s="84">
       <c r="A21" t="inlineStr">
@@ -2139,7 +2123,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22" ht="28" customHeight="1" s="84">
       <c r="A22" t="inlineStr">
@@ -2207,7 +2190,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23" ht="28" customHeight="1" s="84">
       <c r="A23" t="inlineStr">
@@ -2275,7 +2257,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24" ht="28" customHeight="1" s="84">
       <c r="A24" t="inlineStr">
@@ -2343,7 +2324,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25" ht="28" customHeight="1" s="84">
       <c r="A25" t="inlineStr">
@@ -2411,7 +2391,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26" ht="28" customHeight="1" s="84">
       <c r="A26" t="inlineStr">
@@ -2479,7 +2458,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27" ht="28" customHeight="1" s="84">
       <c r="A27" t="inlineStr">
@@ -2547,7 +2525,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28" ht="28" customHeight="1" s="84">
       <c r="A28" t="inlineStr">
@@ -2615,7 +2592,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29" ht="28" customHeight="1" s="84">
       <c r="A29" t="inlineStr">
@@ -2683,7 +2659,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30" ht="28" customHeight="1" s="84">
       <c r="A30" t="inlineStr">
@@ -2751,7 +2726,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31" ht="28" customHeight="1" s="84">
       <c r="A31" t="inlineStr">
@@ -2819,7 +2793,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32" ht="28" customHeight="1" s="84">
       <c r="A32" t="inlineStr">
@@ -2887,7 +2860,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33" ht="28" customHeight="1" s="84">
       <c r="A33" t="inlineStr">
@@ -2955,7 +2927,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34" ht="28" customHeight="1" s="84">
       <c r="A34" t="inlineStr">
@@ -3023,7 +2994,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35" ht="28" customHeight="1" s="84">
       <c r="A35" t="inlineStr">
@@ -3091,7 +3061,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36" ht="28" customHeight="1" s="84">
       <c r="A36" t="inlineStr">
@@ -3159,7 +3128,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37" ht="28" customHeight="1" s="84">
       <c r="A37" t="inlineStr">
@@ -3227,7 +3195,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38" ht="28" customHeight="1" s="84">
       <c r="A38" t="inlineStr">
@@ -3295,7 +3262,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39" ht="28" customHeight="1" s="84">
       <c r="A39" t="inlineStr">
@@ -3363,7 +3329,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40" ht="28" customHeight="1" s="84">
       <c r="A40" t="inlineStr">
@@ -3431,7 +3396,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41" ht="28" customHeight="1" s="84">
       <c r="A41" t="inlineStr">
@@ -3499,7 +3463,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42" ht="28" customHeight="1" s="84">
       <c r="A42" t="inlineStr">
@@ -3567,7 +3530,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43" ht="28" customHeight="1" s="84">
       <c r="A43" t="inlineStr">
@@ -3635,7 +3597,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44" ht="28" customHeight="1" s="84">
       <c r="A44" t="inlineStr">
@@ -3703,7 +3664,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45" ht="28" customHeight="1" s="84">
       <c r="A45" t="inlineStr">
@@ -3771,7 +3731,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46" ht="28" customHeight="1" s="84">
       <c r="A46" t="inlineStr">
@@ -3839,7 +3798,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47" ht="28" customHeight="1" s="84">
       <c r="A47" t="inlineStr">
@@ -3907,7 +3865,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48" ht="28" customHeight="1" s="84">
       <c r="A48" t="inlineStr">
@@ -3975,7 +3932,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49" ht="28" customHeight="1" s="84">
       <c r="A49" t="inlineStr">
@@ -4043,7 +3999,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50" ht="28" customHeight="1" s="84">
       <c r="A50" t="inlineStr">
@@ -4111,7 +4066,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51" ht="28" customHeight="1" s="84">
       <c r="A51" t="inlineStr">
@@ -4179,7 +4133,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52" ht="28" customHeight="1" s="84">
       <c r="A52" t="inlineStr">
@@ -4247,7 +4200,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53" ht="28" customHeight="1" s="84">
       <c r="A53" t="inlineStr">
@@ -4315,7 +4267,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54" ht="28" customHeight="1" s="84">
       <c r="A54" t="inlineStr">
@@ -4383,7 +4334,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55" ht="28" customHeight="1" s="84">
       <c r="A55" t="inlineStr">
@@ -4451,7 +4401,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56" ht="28" customHeight="1" s="84">
       <c r="A56" t="inlineStr">
@@ -4519,7 +4468,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57" ht="28" customHeight="1" s="84">
       <c r="A57" t="inlineStr">
@@ -4587,7 +4535,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58" ht="28" customHeight="1" s="84">
       <c r="A58" t="inlineStr">
@@ -4655,7 +4602,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59" ht="28" customHeight="1" s="84">
       <c r="A59" t="inlineStr">
@@ -4723,7 +4669,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60" ht="28" customHeight="1" s="84">
       <c r="A60" t="inlineStr">
@@ -4791,7 +4736,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61" ht="28" customHeight="1" s="84">
       <c r="A61" t="inlineStr">
@@ -4859,7 +4803,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62" ht="28" customHeight="1" s="84">
       <c r="A62" t="inlineStr">
@@ -4927,7 +4870,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63" ht="28" customHeight="1" s="84">
       <c r="A63" t="inlineStr">
@@ -4995,7 +4937,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64" ht="28" customHeight="1" s="84">
       <c r="A64" t="inlineStr">
@@ -5063,7 +5004,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65" ht="28" customHeight="1" s="84">
       <c r="A65" t="inlineStr">
@@ -5131,7 +5071,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66" ht="28" customHeight="1" s="84">
       <c r="A66" t="inlineStr">
@@ -5199,7 +5138,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67" ht="28" customHeight="1" s="84">
       <c r="A67" t="inlineStr">
@@ -5267,7 +5205,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68" ht="28" customHeight="1" s="84">
       <c r="A68" t="inlineStr">
@@ -5335,7 +5272,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69" ht="28" customHeight="1" s="84">
       <c r="A69" t="inlineStr">
@@ -5403,7 +5339,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70" ht="28" customHeight="1" s="84">
       <c r="A70" t="inlineStr">
@@ -5471,7 +5406,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71" ht="28" customHeight="1" s="84">
       <c r="A71" t="inlineStr">
@@ -5539,7 +5473,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72" ht="28" customHeight="1" s="84">
       <c r="A72" t="inlineStr">
@@ -5607,7 +5540,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73" ht="28" customHeight="1" s="84">
       <c r="A73" t="inlineStr">
@@ -5675,7 +5607,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74" ht="28" customHeight="1" s="84">
       <c r="A74" t="inlineStr">
@@ -5743,7 +5674,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75" ht="28" customHeight="1" s="84">
       <c r="A75" t="inlineStr">
@@ -5811,7 +5741,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76" ht="28" customHeight="1" s="84">
       <c r="A76" t="inlineStr">
@@ -5879,7 +5808,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77" ht="28" customHeight="1" s="84">
       <c r="A77" t="inlineStr">
@@ -5947,7 +5875,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78" ht="28" customHeight="1" s="84">
       <c r="A78" t="inlineStr">
@@ -6015,7 +5942,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79" ht="28" customHeight="1" s="84">
       <c r="A79" t="inlineStr">
@@ -6083,7 +6009,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80" ht="28" customHeight="1" s="84">
       <c r="A80" t="inlineStr">
@@ -6151,7 +6076,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81" ht="28" customHeight="1" s="84">
       <c r="A81" t="inlineStr">
@@ -6219,7 +6143,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82" ht="28" customHeight="1" s="84">
       <c r="A82" t="inlineStr">
@@ -6287,7 +6210,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83" ht="28" customHeight="1" s="84">
       <c r="A83" t="inlineStr">
@@ -6355,7 +6277,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
     </row>
     <row r="84" ht="28" customHeight="1" s="84">
       <c r="A84" t="inlineStr">
@@ -6423,7 +6344,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85" ht="28" customHeight="1" s="84">
       <c r="A85" t="inlineStr">
@@ -6491,7 +6411,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
     </row>
     <row r="86" ht="28" customHeight="1" s="84">
       <c r="A86" t="inlineStr">
@@ -6559,7 +6478,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87" ht="28" customHeight="1" s="84">
       <c r="A87" t="inlineStr">
@@ -6627,7 +6545,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88" ht="28" customHeight="1" s="84">
       <c r="A88" t="inlineStr">
@@ -6695,7 +6612,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89" ht="28" customHeight="1" s="84">
       <c r="A89" t="inlineStr">
@@ -6763,7 +6679,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90" ht="28" customHeight="1" s="84">
       <c r="A90" t="inlineStr">
@@ -6831,7 +6746,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr"/>
     </row>
     <row r="91" ht="28" customHeight="1" s="84">
       <c r="A91" t="inlineStr">
@@ -6899,7 +6813,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
     </row>
     <row r="92" ht="28" customHeight="1" s="84">
       <c r="A92" t="inlineStr">
@@ -6967,7 +6880,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
     </row>
     <row r="93" ht="28" customHeight="1" s="84">
       <c r="A93" t="inlineStr">
@@ -7035,7 +6947,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
     </row>
     <row r="94" ht="28" customHeight="1" s="84">
       <c r="A94" t="inlineStr">
@@ -7103,7 +7014,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95" ht="28" customHeight="1" s="84">
       <c r="A95" t="inlineStr">
@@ -7171,7 +7081,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96" ht="28" customHeight="1" s="84">
       <c r="A96" t="inlineStr">
@@ -7239,7 +7148,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr"/>
     </row>
     <row r="97" ht="28" customHeight="1" s="84">
       <c r="A97" t="inlineStr">
@@ -7307,7 +7215,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98" ht="28" customHeight="1" s="84">
       <c r="A98" t="inlineStr">
@@ -7375,7 +7282,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99" ht="28" customHeight="1" s="84">
       <c r="A99" t="inlineStr">
@@ -7443,7 +7349,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100" ht="28" customHeight="1" s="84">
       <c r="A100" t="inlineStr">
@@ -7511,7 +7416,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101" ht="28" customHeight="1" s="84">
       <c r="A101" t="inlineStr">
@@ -7579,7 +7483,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
     </row>
     <row r="102" ht="28" customHeight="1" s="84">
       <c r="A102" t="inlineStr">
@@ -7647,7 +7550,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr"/>
     </row>
     <row r="103" ht="28" customHeight="1" s="84">
       <c r="A103" t="inlineStr">
@@ -7715,7 +7617,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr"/>
     </row>
     <row r="104" ht="28" customHeight="1" s="84">
       <c r="A104" t="inlineStr">
@@ -7783,7 +7684,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr"/>
     </row>
     <row r="105" ht="28" customHeight="1" s="84">
       <c r="A105" t="inlineStr">
@@ -7851,7 +7751,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr"/>
     </row>
     <row r="106" ht="28" customHeight="1" s="84">
       <c r="A106" t="inlineStr">
@@ -7919,7 +7818,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr"/>
     </row>
     <row r="107" ht="28" customHeight="1" s="84">
       <c r="A107" t="inlineStr">
@@ -7987,7 +7885,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr"/>
     </row>
     <row r="108" ht="28" customHeight="1" s="84">
       <c r="A108" t="inlineStr">
@@ -8055,7 +7952,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr"/>
     </row>
     <row r="109" ht="28" customHeight="1" s="84">
       <c r="A109" t="inlineStr">
@@ -8123,7 +8019,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P109" t="inlineStr"/>
     </row>
     <row r="110" ht="28" customHeight="1" s="84">
       <c r="A110" t="inlineStr">
@@ -8191,7 +8086,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P110" t="inlineStr"/>
     </row>
     <row r="111" ht="28" customHeight="1" s="84">
       <c r="A111" t="inlineStr">
@@ -8259,7 +8153,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P111" t="inlineStr"/>
     </row>
     <row r="112" ht="28" customHeight="1" s="84">
       <c r="A112" t="inlineStr">
@@ -8327,7 +8220,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P112" t="inlineStr"/>
     </row>
     <row r="113" ht="28" customHeight="1" s="84">
       <c r="A113" t="inlineStr">
@@ -8395,7 +8287,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr"/>
     </row>
     <row r="114" ht="28" customHeight="1" s="84">
       <c r="A114" t="inlineStr">
@@ -8463,7 +8354,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P114" t="inlineStr"/>
     </row>
     <row r="115" ht="28" customHeight="1" s="84">
       <c r="A115" t="inlineStr">
@@ -8531,7 +8421,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116" ht="28" customHeight="1" s="84">
       <c r="A116" t="inlineStr">
@@ -8599,7 +8488,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117" ht="28" customHeight="1" s="84">
       <c r="A117" t="inlineStr">
@@ -8667,7 +8555,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118" ht="28" customHeight="1" s="84">
       <c r="A118" t="inlineStr">
@@ -8735,7 +8622,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P118" t="inlineStr"/>
     </row>
     <row r="119" ht="28" customHeight="1" s="84">
       <c r="A119" t="inlineStr">
@@ -8803,7 +8689,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P119" t="inlineStr"/>
     </row>
     <row r="120" ht="28" customHeight="1" s="84">
       <c r="A120" t="inlineStr">
@@ -8871,7 +8756,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P120" t="inlineStr"/>
     </row>
     <row r="121" ht="28" customHeight="1" s="84">
       <c r="A121" t="inlineStr">
@@ -8939,7 +8823,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P121" t="inlineStr"/>
     </row>
     <row r="122" ht="28" customHeight="1" s="84">
       <c r="A122" t="inlineStr">
@@ -9007,7 +8890,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr"/>
     </row>
     <row r="123" ht="28" customHeight="1" s="84">
       <c r="A123" t="inlineStr">
@@ -9075,7 +8957,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P123" t="inlineStr"/>
     </row>
     <row r="124" ht="28" customHeight="1" s="84">
       <c r="A124" t="inlineStr">
@@ -9143,7 +9024,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr"/>
     </row>
     <row r="125" ht="28" customHeight="1" s="84">
       <c r="A125" t="inlineStr">
@@ -9211,7 +9091,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P125" t="inlineStr"/>
     </row>
     <row r="126" ht="28" customHeight="1" s="84">
       <c r="A126" t="inlineStr">
@@ -9279,7 +9158,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P126" t="inlineStr"/>
     </row>
     <row r="127" ht="28" customHeight="1" s="84">
       <c r="A127" t="inlineStr">
@@ -9347,7 +9225,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P127" t="inlineStr"/>
     </row>
     <row r="128" ht="28" customHeight="1" s="84">
       <c r="A128" t="inlineStr">
@@ -9415,7 +9292,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr"/>
     </row>
     <row r="129" ht="28" customHeight="1" s="84">
       <c r="A129" t="inlineStr">
@@ -9483,7 +9359,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P129" t="inlineStr"/>
     </row>
     <row r="130" ht="28" customHeight="1" s="84">
       <c r="A130" t="inlineStr">
@@ -9551,7 +9426,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P130" t="inlineStr"/>
     </row>
     <row r="131" ht="28" customHeight="1" s="84">
       <c r="A131" t="inlineStr">
@@ -9619,7 +9493,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P131" t="inlineStr"/>
     </row>
     <row r="132" ht="28" customHeight="1" s="84">
       <c r="A132" t="inlineStr">
@@ -9687,7 +9560,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P132" t="inlineStr"/>
     </row>
     <row r="133" ht="28" customHeight="1" s="84">
       <c r="A133" t="inlineStr">
@@ -9755,7 +9627,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P133" t="inlineStr"/>
     </row>
     <row r="134" ht="28" customHeight="1" s="84">
       <c r="A134" t="inlineStr">
@@ -9823,7 +9694,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P134" t="inlineStr"/>
     </row>
     <row r="135" ht="28" customHeight="1" s="84">
       <c r="A135" t="inlineStr">
@@ -9891,7 +9761,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P135" t="inlineStr"/>
     </row>
     <row r="136" ht="28" customHeight="1" s="84">
       <c r="A136" t="inlineStr">
@@ -9959,7 +9828,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P136" t="inlineStr"/>
     </row>
     <row r="137" ht="28" customHeight="1" s="84">
       <c r="A137" t="inlineStr">
@@ -10027,7 +9895,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138" ht="28" customHeight="1" s="84">
       <c r="A138" t="inlineStr">
@@ -10095,7 +9962,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139" ht="28" customHeight="1" s="84">
       <c r="A139" t="inlineStr">
@@ -10163,7 +10029,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140" ht="28" customHeight="1" s="84">
       <c r="A140" t="inlineStr">
@@ -10231,7 +10096,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141" ht="28" customHeight="1" s="84">
       <c r="A141" t="inlineStr">
@@ -10299,7 +10163,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P141" t="inlineStr"/>
     </row>
     <row r="142" ht="28" customHeight="1" s="84">
       <c r="A142" t="inlineStr">
@@ -10367,7 +10230,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P142" t="inlineStr"/>
     </row>
     <row r="143" ht="28" customHeight="1" s="84">
       <c r="A143" t="inlineStr">
@@ -10435,7 +10297,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr"/>
     </row>
     <row r="144" ht="28" customHeight="1" s="84">
       <c r="A144" t="inlineStr">
@@ -10503,7 +10364,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P144" t="inlineStr"/>
     </row>
     <row r="145" ht="28" customHeight="1" s="84">
       <c r="A145" t="inlineStr">
@@ -10571,7 +10431,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P145" t="inlineStr"/>
     </row>
     <row r="146" ht="28" customHeight="1" s="84">
       <c r="A146" t="inlineStr">
@@ -10639,7 +10498,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P146" t="inlineStr"/>
     </row>
     <row r="147" ht="28" customHeight="1" s="84">
       <c r="A147" t="inlineStr">
@@ -10707,7 +10565,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P147" t="inlineStr"/>
     </row>
     <row r="148" ht="28" customHeight="1" s="84">
       <c r="A148" t="inlineStr">
@@ -10775,7 +10632,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P148" t="inlineStr"/>
     </row>
     <row r="149" ht="28" customHeight="1" s="84">
       <c r="A149" t="inlineStr">
@@ -10843,7 +10699,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P149" t="inlineStr"/>
     </row>
     <row r="150" ht="28" customHeight="1" s="84">
       <c r="A150" t="inlineStr">
@@ -10911,7 +10766,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151" ht="28" customHeight="1" s="84">
       <c r="A151" t="inlineStr">
@@ -10979,7 +10833,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P151" t="inlineStr"/>
     </row>
     <row r="152" ht="28" customHeight="1" s="84">
       <c r="A152" t="inlineStr">
@@ -11047,7 +10900,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P152" t="inlineStr"/>
     </row>
     <row r="153" ht="28" customHeight="1" s="84">
       <c r="A153" t="inlineStr">
@@ -11115,7 +10967,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154" ht="28" customHeight="1" s="84">
       <c r="A154" t="inlineStr">
@@ -11183,7 +11034,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155" ht="28" customHeight="1" s="84">
       <c r="A155" t="inlineStr">
@@ -11251,7 +11101,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr"/>
     </row>
     <row r="156" ht="28" customHeight="1" s="84">
       <c r="A156" t="inlineStr">
@@ -11319,7 +11168,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P156" t="inlineStr"/>
     </row>
     <row r="157" ht="28" customHeight="1" s="84">
       <c r="A157" t="inlineStr">
@@ -11387,7 +11235,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr"/>
     </row>
     <row r="158" ht="28" customHeight="1" s="84">
       <c r="A158" t="inlineStr">
@@ -11455,7 +11302,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159" ht="28" customHeight="1" s="84">
       <c r="A159" t="inlineStr">
@@ -11523,7 +11369,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160" ht="28" customHeight="1" s="84">
       <c r="A160" t="inlineStr">
@@ -11591,7 +11436,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P160" t="inlineStr"/>
     </row>
     <row r="161" ht="28" customHeight="1" s="84">
       <c r="A161" t="inlineStr">
@@ -11659,7 +11503,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P161" t="inlineStr"/>
     </row>
     <row r="162" ht="28" customHeight="1" s="84">
       <c r="A162" t="inlineStr">
@@ -11727,7 +11570,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P162" t="inlineStr"/>
     </row>
     <row r="163" ht="28" customHeight="1" s="84">
       <c r="A163" t="inlineStr">
@@ -11795,7 +11637,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P163" t="inlineStr"/>
     </row>
     <row r="164" ht="28" customHeight="1" s="84">
       <c r="A164" t="inlineStr">
@@ -11863,7 +11704,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P164" t="inlineStr"/>
     </row>
     <row r="165" ht="28" customHeight="1" s="84">
       <c r="A165" t="inlineStr">
@@ -11931,7 +11771,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P165" t="inlineStr"/>
     </row>
     <row r="166" ht="28" customHeight="1" s="84">
       <c r="A166" t="inlineStr">
@@ -11999,7 +11838,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P166" t="inlineStr"/>
     </row>
     <row r="167" ht="28" customHeight="1" s="84">
       <c r="A167" t="inlineStr">
@@ -12067,7 +11905,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168" ht="28" customHeight="1" s="84">
       <c r="A168" t="inlineStr">
@@ -12135,7 +11972,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P168" t="inlineStr"/>
     </row>
     <row r="169" ht="28" customHeight="1" s="84">
       <c r="A169" t="inlineStr">
@@ -12203,7 +12039,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170" ht="28" customHeight="1" s="84">
       <c r="A170" t="inlineStr">
@@ -12271,7 +12106,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P170" t="inlineStr"/>
     </row>
     <row r="171" ht="28" customHeight="1" s="84">
       <c r="A171" t="inlineStr">
@@ -12339,7 +12173,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr"/>
     </row>
     <row r="172" ht="28" customHeight="1" s="84">
       <c r="A172" t="inlineStr">
@@ -12407,7 +12240,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P172" t="inlineStr"/>
     </row>
     <row r="173" ht="28" customHeight="1" s="84">
       <c r="A173" t="inlineStr">
@@ -12475,7 +12307,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P173" t="inlineStr"/>
     </row>
     <row r="174" ht="28" customHeight="1" s="84">
       <c r="A174" t="inlineStr">
@@ -12543,7 +12374,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P174" t="inlineStr"/>
     </row>
     <row r="175" ht="28" customHeight="1" s="84">
       <c r="A175" t="inlineStr">
@@ -12611,7 +12441,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P175" t="inlineStr"/>
     </row>
     <row r="176" ht="28" customHeight="1" s="84">
       <c r="A176" t="inlineStr">
@@ -12679,7 +12508,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P176" t="inlineStr"/>
     </row>
     <row r="177" ht="28" customHeight="1" s="84">
       <c r="A177" t="inlineStr">
@@ -12747,7 +12575,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P177" t="inlineStr"/>
     </row>
     <row r="178" ht="28" customHeight="1" s="84">
       <c r="A178" t="inlineStr">
@@ -12815,7 +12642,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P178" t="inlineStr"/>
     </row>
     <row r="179" ht="28" customHeight="1" s="84">
       <c r="A179" t="inlineStr">
@@ -12883,7 +12709,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180" ht="28" customHeight="1" s="84">
       <c r="A180" t="inlineStr">
@@ -12951,7 +12776,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P180" t="inlineStr"/>
     </row>
     <row r="181" ht="28" customHeight="1" s="84">
       <c r="A181" t="inlineStr">
@@ -13019,7 +12843,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P181" t="inlineStr"/>
     </row>
     <row r="182" ht="28" customHeight="1" s="84">
       <c r="A182" t="inlineStr">
@@ -13087,7 +12910,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P182" t="inlineStr"/>
     </row>
     <row r="183" ht="28" customHeight="1" s="84">
       <c r="A183" t="inlineStr">
@@ -13155,7 +12977,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P183" t="inlineStr"/>
     </row>
     <row r="184" ht="28" customHeight="1" s="84">
       <c r="A184" t="inlineStr">
@@ -13223,7 +13044,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P184" t="inlineStr"/>
     </row>
     <row r="185" ht="28" customHeight="1" s="84">
       <c r="A185" t="inlineStr">
@@ -13291,7 +13111,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P185" t="inlineStr"/>
     </row>
     <row r="186" ht="28" customHeight="1" s="84">
       <c r="A186" t="inlineStr">
@@ -13359,7 +13178,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P186" t="inlineStr"/>
     </row>
     <row r="187" ht="28" customHeight="1" s="84">
       <c r="A187" t="inlineStr">
@@ -13427,7 +13245,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P187" t="inlineStr"/>
     </row>
     <row r="188" ht="28" customHeight="1" s="84">
       <c r="A188" t="inlineStr">
@@ -13495,7 +13312,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P188" t="inlineStr"/>
     </row>
     <row r="189" ht="28" customHeight="1" s="84">
       <c r="A189" t="inlineStr">
@@ -13563,7 +13379,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P189" t="inlineStr"/>
     </row>
     <row r="190" ht="28" customHeight="1" s="84">
       <c r="A190" t="inlineStr">
@@ -13631,7 +13446,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P190" t="inlineStr"/>
     </row>
     <row r="191" ht="28" customHeight="1" s="84">
       <c r="A191" t="inlineStr">
@@ -13699,7 +13513,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P191" t="inlineStr"/>
     </row>
     <row r="192" ht="28" customHeight="1" s="84">
       <c r="A192" t="inlineStr">
@@ -13767,7 +13580,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P192" t="inlineStr"/>
     </row>
     <row r="193" ht="28" customHeight="1" s="84">
       <c r="A193" t="inlineStr">
@@ -13835,7 +13647,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P193" t="inlineStr"/>
     </row>
     <row r="194" ht="28" customHeight="1" s="84">
       <c r="A194" t="inlineStr">
@@ -13903,7 +13714,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P194" t="inlineStr"/>
     </row>
     <row r="195" ht="28" customHeight="1" s="84">
       <c r="A195" t="inlineStr">
@@ -13971,7 +13781,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P195" t="inlineStr"/>
     </row>
     <row r="196" ht="28" customHeight="1" s="84">
       <c r="A196" t="inlineStr">
@@ -14039,7 +13848,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P196" t="inlineStr"/>
     </row>
     <row r="197" ht="28" customHeight="1" s="84">
       <c r="A197" t="inlineStr">
@@ -14107,7 +13915,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P197" t="inlineStr"/>
     </row>
     <row r="198" ht="28" customHeight="1" s="84">
       <c r="A198" t="inlineStr">
@@ -14175,7 +13982,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P198" t="inlineStr"/>
     </row>
     <row r="199" ht="28" customHeight="1" s="84">
       <c r="A199" t="inlineStr">
@@ -14243,7 +14049,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P199" t="inlineStr"/>
     </row>
     <row r="200" ht="28" customHeight="1" s="84">
       <c r="A200" t="inlineStr">
@@ -14311,7 +14116,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P200" t="inlineStr"/>
     </row>
     <row r="201" ht="28" customHeight="1" s="84">
       <c r="A201" t="inlineStr">
@@ -14379,7 +14183,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P201" t="inlineStr"/>
     </row>
     <row r="202" ht="28" customHeight="1" s="84">
       <c r="A202" t="inlineStr">
@@ -14447,7 +14250,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P202" t="inlineStr"/>
     </row>
     <row r="203" ht="28" customHeight="1" s="84">
       <c r="A203" t="inlineStr">
@@ -14515,7 +14317,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P203" t="inlineStr"/>
     </row>
     <row r="204" ht="28" customHeight="1" s="84">
       <c r="A204" t="inlineStr">
@@ -14583,7 +14384,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205" ht="28" customHeight="1" s="84">
       <c r="A205" t="inlineStr">
@@ -14651,7 +14451,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P205" t="inlineStr"/>
     </row>
     <row r="206" ht="28" customHeight="1" s="84">
       <c r="A206" t="inlineStr">
@@ -14719,7 +14518,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P206" t="inlineStr"/>
     </row>
     <row r="207" ht="28" customHeight="1" s="84">
       <c r="A207" t="inlineStr">
@@ -14787,7 +14585,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P207" t="inlineStr"/>
     </row>
     <row r="208" ht="28" customHeight="1" s="84">
       <c r="A208" t="inlineStr">
@@ -14855,7 +14652,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P208" t="inlineStr"/>
     </row>
     <row r="209" ht="28" customHeight="1" s="84">
       <c r="A209" t="inlineStr">
@@ -14923,7 +14719,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P209" t="inlineStr"/>
     </row>
     <row r="210" ht="28" customHeight="1" s="84">
       <c r="A210" t="inlineStr">
@@ -14991,7 +14786,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P210" t="inlineStr"/>
     </row>
     <row r="211" ht="28" customHeight="1" s="84">
       <c r="A211" t="inlineStr">
@@ -15059,7 +14853,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P211" t="inlineStr"/>
     </row>
     <row r="212" ht="28" customHeight="1" s="84">
       <c r="A212" t="inlineStr">
@@ -15127,7 +14920,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P212" t="inlineStr"/>
     </row>
     <row r="213" ht="28" customHeight="1" s="84">
       <c r="A213" t="inlineStr">
@@ -15195,7 +14987,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P213" t="inlineStr"/>
     </row>
     <row r="214" ht="28" customHeight="1" s="84">
       <c r="A214" t="inlineStr">
@@ -15263,7 +15054,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P214" t="inlineStr"/>
     </row>
     <row r="215" ht="28" customHeight="1" s="84">
       <c r="A215" t="inlineStr">
@@ -15331,7 +15121,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P215" t="inlineStr"/>
     </row>
     <row r="216" ht="28" customHeight="1" s="84">
       <c r="A216" t="inlineStr">
@@ -15399,7 +15188,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P216" t="inlineStr"/>
     </row>
     <row r="217" ht="28" customHeight="1" s="84">
       <c r="A217" t="inlineStr">
@@ -15467,7 +15255,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P217" t="inlineStr"/>
     </row>
     <row r="218" ht="28" customHeight="1" s="84">
       <c r="A218" t="inlineStr">
@@ -15535,7 +15322,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P218" t="inlineStr"/>
     </row>
     <row r="219" ht="28" customHeight="1" s="84">
       <c r="A219" t="inlineStr">
@@ -15603,7 +15389,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P219" t="inlineStr"/>
     </row>
     <row r="220" ht="28" customHeight="1" s="84">
       <c r="A220" t="inlineStr">
@@ -15671,7 +15456,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P220" t="inlineStr"/>
     </row>
     <row r="221" ht="28" customHeight="1" s="84">
       <c r="A221" t="inlineStr">
@@ -15739,7 +15523,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P221" t="inlineStr"/>
     </row>
     <row r="222" ht="28" customHeight="1" s="84">
       <c r="A222" t="inlineStr">
@@ -15807,7 +15590,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P222" t="inlineStr"/>
     </row>
     <row r="223" ht="28" customHeight="1" s="84">
       <c r="A223" t="inlineStr">
@@ -15875,7 +15657,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P223" t="inlineStr"/>
     </row>
     <row r="224" ht="28" customHeight="1" s="84">
       <c r="A224" t="inlineStr">
@@ -15943,7 +15724,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P224" t="inlineStr"/>
     </row>
     <row r="225" ht="28" customHeight="1" s="84">
       <c r="A225" t="inlineStr">
@@ -16011,7 +15791,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P225" t="inlineStr"/>
     </row>
     <row r="226" ht="28" customHeight="1" s="84">
       <c r="A226" t="inlineStr">
@@ -16079,7 +15858,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P226" t="inlineStr"/>
     </row>
     <row r="227" ht="28" customHeight="1" s="84">
       <c r="A227" t="inlineStr">
@@ -16147,7 +15925,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P227" t="inlineStr"/>
     </row>
     <row r="228" ht="28" customHeight="1" s="84">
       <c r="A228" t="inlineStr">
@@ -16215,7 +15992,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P228" t="inlineStr"/>
     </row>
     <row r="229" ht="28" customHeight="1" s="84">
       <c r="A229" t="inlineStr">
@@ -16283,7 +16059,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P229" t="inlineStr"/>
     </row>
     <row r="230" ht="28" customHeight="1" s="84">
       <c r="A230" t="inlineStr">
@@ -16351,7 +16126,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P230" t="inlineStr"/>
     </row>
     <row r="231" ht="28" customHeight="1" s="84">
       <c r="A231" t="inlineStr">
@@ -16419,7 +16193,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P231" t="inlineStr"/>
     </row>
     <row r="232" ht="28" customHeight="1" s="84">
       <c r="A232" t="inlineStr">
@@ -16487,7 +16260,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P232" t="inlineStr"/>
     </row>
     <row r="233" ht="28" customHeight="1" s="84">
       <c r="A233" t="inlineStr">
@@ -16555,7 +16327,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P233" t="inlineStr"/>
     </row>
     <row r="234" ht="28" customHeight="1" s="84">
       <c r="A234" t="inlineStr">
@@ -16623,7 +16394,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P234" t="inlineStr"/>
     </row>
     <row r="235" ht="28" customHeight="1" s="84">
       <c r="A235" t="inlineStr">
@@ -16691,7 +16461,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P235" t="inlineStr"/>
     </row>
     <row r="236" ht="28" customHeight="1" s="84">
       <c r="A236" t="inlineStr">
@@ -16759,7 +16528,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P236" t="inlineStr"/>
     </row>
     <row r="237" ht="28" customHeight="1" s="84">
       <c r="A237" t="inlineStr">
@@ -16827,7 +16595,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P237" t="inlineStr"/>
     </row>
     <row r="238" ht="28" customHeight="1" s="84">
       <c r="A238" t="inlineStr">
@@ -16895,7 +16662,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P238" t="inlineStr"/>
     </row>
     <row r="239" ht="28" customHeight="1" s="84">
       <c r="A239" t="inlineStr">
@@ -16963,7 +16729,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P239" t="inlineStr"/>
     </row>
     <row r="240" ht="28" customHeight="1" s="84">
       <c r="A240" t="inlineStr">
@@ -17031,7 +16796,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P240" t="inlineStr"/>
     </row>
     <row r="241" ht="28" customHeight="1" s="84">
       <c r="A241" t="inlineStr">
@@ -17099,7 +16863,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P241" t="inlineStr"/>
     </row>
     <row r="242" ht="28" customHeight="1" s="84">
       <c r="A242" t="inlineStr">
@@ -17167,7 +16930,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P242" t="inlineStr"/>
     </row>
     <row r="243" ht="28" customHeight="1" s="84">
       <c r="A243" t="inlineStr">
@@ -17235,7 +16997,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P243" t="inlineStr"/>
     </row>
     <row r="244" ht="28" customHeight="1" s="84">
       <c r="A244" t="inlineStr">
@@ -17303,7 +17064,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P244" t="inlineStr"/>
     </row>
     <row r="245" ht="28" customHeight="1" s="84">
       <c r="A245" t="inlineStr">
@@ -17371,7 +17131,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P245" t="inlineStr"/>
     </row>
     <row r="246" ht="28" customHeight="1" s="84">
       <c r="A246" t="inlineStr">
@@ -17439,7 +17198,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P246" t="inlineStr"/>
     </row>
     <row r="247" ht="28" customHeight="1" s="84">
       <c r="A247" t="inlineStr">
@@ -17507,7 +17265,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P247" t="inlineStr"/>
     </row>
     <row r="248" ht="28" customHeight="1" s="84">
       <c r="A248" t="inlineStr">
@@ -17575,7 +17332,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P248" t="inlineStr"/>
     </row>
     <row r="249" ht="28" customHeight="1" s="84">
       <c r="A249" t="inlineStr">
@@ -17643,7 +17399,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P249" t="inlineStr"/>
     </row>
     <row r="250" ht="28" customHeight="1" s="84">
       <c r="A250" t="inlineStr">
@@ -17711,7 +17466,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P250" t="inlineStr"/>
     </row>
     <row r="251" ht="28" customHeight="1" s="84">
       <c r="A251" t="inlineStr">
@@ -17779,7 +17533,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P251" t="inlineStr"/>
     </row>
     <row r="252" ht="28" customHeight="1" s="84">
       <c r="A252" t="inlineStr">
@@ -17847,7 +17600,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P252" t="inlineStr"/>
     </row>
     <row r="253" ht="28" customHeight="1" s="84">
       <c r="A253" t="inlineStr">
@@ -17915,7 +17667,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P253" t="inlineStr"/>
     </row>
     <row r="254" ht="28" customHeight="1" s="84">
       <c r="A254" t="inlineStr">
@@ -17983,7 +17734,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P254" t="inlineStr"/>
     </row>
     <row r="255" ht="28" customHeight="1" s="84">
       <c r="A255" t="inlineStr">
@@ -18051,7 +17801,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P255" t="inlineStr"/>
     </row>
     <row r="256" ht="28" customHeight="1" s="84">
       <c r="A256" t="inlineStr">
@@ -18119,7 +17868,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P256" t="inlineStr"/>
     </row>
     <row r="257" ht="28" customHeight="1" s="84">
       <c r="A257" t="inlineStr">
@@ -18187,7 +17935,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P257" t="inlineStr"/>
     </row>
     <row r="258" ht="28" customHeight="1" s="84">
       <c r="A258" t="inlineStr">
@@ -18255,7 +18002,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P258" t="inlineStr"/>
     </row>
     <row r="259" ht="28" customHeight="1" s="84">
       <c r="A259" t="inlineStr">
@@ -18323,7 +18069,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P259" t="inlineStr"/>
     </row>
     <row r="260" ht="28" customHeight="1" s="84">
       <c r="A260" t="inlineStr">
@@ -18391,7 +18136,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P260" t="inlineStr"/>
     </row>
     <row r="261" ht="28" customHeight="1" s="84">
       <c r="A261" t="inlineStr">
@@ -18459,7 +18203,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P261" t="inlineStr"/>
     </row>
     <row r="262" ht="28" customHeight="1" s="84">
       <c r="A262" t="inlineStr">
@@ -18527,7 +18270,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P262" t="inlineStr"/>
     </row>
     <row r="263" ht="28" customHeight="1" s="84">
       <c r="A263" t="inlineStr">
@@ -18595,7 +18337,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P263" t="inlineStr"/>
     </row>
     <row r="264" ht="28" customHeight="1" s="84">
       <c r="A264" t="inlineStr">
@@ -18663,7 +18404,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P264" t="inlineStr"/>
     </row>
     <row r="265" ht="28" customHeight="1" s="84">
       <c r="A265" t="inlineStr">
@@ -18731,7 +18471,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P265" t="inlineStr"/>
     </row>
     <row r="266" ht="28" customHeight="1" s="84">
       <c r="A266" t="inlineStr">
@@ -18799,7 +18538,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P266" t="inlineStr"/>
     </row>
     <row r="267" ht="28" customHeight="1" s="84">
       <c r="A267" t="inlineStr">
@@ -18867,7 +18605,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P267" t="inlineStr"/>
     </row>
     <row r="268" ht="28" customHeight="1" s="84">
       <c r="A268" t="inlineStr">
@@ -18935,7 +18672,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P268" t="inlineStr"/>
     </row>
     <row r="269" ht="28" customHeight="1" s="84">
       <c r="A269" t="inlineStr">
@@ -19003,7 +18739,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P269" t="inlineStr"/>
     </row>
     <row r="270" ht="28" customHeight="1" s="84">
       <c r="A270" t="inlineStr">
@@ -19071,7 +18806,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P270" t="inlineStr"/>
     </row>
     <row r="271" ht="28" customHeight="1" s="84">
       <c r="A271" t="inlineStr">
@@ -19139,7 +18873,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P271" t="inlineStr"/>
     </row>
     <row r="272" ht="28" customHeight="1" s="84">
       <c r="A272" t="inlineStr">
@@ -19207,7 +18940,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P272" t="inlineStr"/>
     </row>
     <row r="273" ht="28" customHeight="1" s="84">
       <c r="A273" t="inlineStr">
@@ -19275,7 +19007,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P273" t="inlineStr"/>
     </row>
     <row r="274" ht="28" customHeight="1" s="84">
       <c r="A274" t="inlineStr">
@@ -19343,7 +19074,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P274" t="inlineStr"/>
     </row>
     <row r="275" ht="28" customHeight="1" s="84">
       <c r="A275" t="inlineStr">
@@ -19411,7 +19141,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P275" t="inlineStr"/>
     </row>
     <row r="276" ht="28" customHeight="1" s="84">
       <c r="A276" t="inlineStr">
@@ -19479,7 +19208,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P276" t="inlineStr"/>
     </row>
     <row r="277" ht="28" customHeight="1" s="84">
       <c r="A277" t="inlineStr">
@@ -19547,7 +19275,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P277" t="inlineStr"/>
     </row>
     <row r="278" ht="28" customHeight="1" s="84">
       <c r="A278" t="inlineStr">
@@ -19615,7 +19342,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P278" t="inlineStr"/>
     </row>
     <row r="279" ht="28" customHeight="1" s="84">
       <c r="A279" t="inlineStr">
@@ -19683,7 +19409,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P279" t="inlineStr"/>
     </row>
     <row r="280" ht="28" customHeight="1" s="84">
       <c r="A280" t="inlineStr">
@@ -19751,7 +19476,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P280" t="inlineStr"/>
     </row>
     <row r="281" ht="28" customHeight="1" s="84">
       <c r="A281" t="inlineStr">
@@ -19819,7 +19543,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P281" t="inlineStr"/>
     </row>
     <row r="282" ht="28" customHeight="1" s="84">
       <c r="A282" t="inlineStr">
@@ -19887,7 +19610,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P282" t="inlineStr"/>
     </row>
     <row r="283" ht="28" customHeight="1" s="84">
       <c r="A283" t="inlineStr">
@@ -19955,7 +19677,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P283" t="inlineStr"/>
     </row>
     <row r="284" ht="28" customHeight="1" s="84">
       <c r="A284" t="inlineStr">
@@ -20023,7 +19744,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P284" t="inlineStr"/>
     </row>
     <row r="285" ht="28" customHeight="1" s="84">
       <c r="A285" t="inlineStr">
@@ -20091,7 +19811,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P285" t="inlineStr"/>
     </row>
     <row r="286" ht="28" customHeight="1" s="84">
       <c r="A286" t="inlineStr">
@@ -20159,7 +19878,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P286" t="inlineStr"/>
     </row>
     <row r="287" ht="28" customHeight="1" s="84">
       <c r="A287" t="inlineStr">
@@ -20227,7 +19945,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P287" t="inlineStr"/>
     </row>
     <row r="288" ht="28" customHeight="1" s="84">
       <c r="A288" t="inlineStr">
@@ -20295,7 +20012,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P288" t="inlineStr"/>
     </row>
     <row r="289" ht="28" customHeight="1" s="84">
       <c r="A289" t="inlineStr">
@@ -20363,7 +20079,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P289" t="inlineStr"/>
     </row>
     <row r="290" ht="28" customHeight="1" s="84">
       <c r="A290" t="inlineStr">
@@ -20431,7 +20146,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P290" t="inlineStr"/>
     </row>
     <row r="291" ht="28" customHeight="1" s="84">
       <c r="A291" t="inlineStr">
@@ -20499,7 +20213,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P291" t="inlineStr"/>
     </row>
     <row r="292" ht="28" customHeight="1" s="84">
       <c r="A292" t="inlineStr">
@@ -20567,7 +20280,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P292" t="inlineStr"/>
     </row>
     <row r="293" ht="28" customHeight="1" s="84">
       <c r="A293" t="inlineStr">
@@ -20635,7 +20347,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P293" t="inlineStr"/>
     </row>
     <row r="294" ht="28" customHeight="1" s="84">
       <c r="A294" t="inlineStr">
@@ -20703,7 +20414,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P294" t="inlineStr"/>
     </row>
     <row r="295" ht="28" customHeight="1" s="84">
       <c r="A295" t="inlineStr">
@@ -20771,7 +20481,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P295" t="inlineStr"/>
     </row>
     <row r="296" ht="28" customHeight="1" s="84">
       <c r="A296" t="inlineStr">
@@ -20839,7 +20548,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P296" t="inlineStr"/>
     </row>
     <row r="297" ht="28" customHeight="1" s="84">
       <c r="A297" t="inlineStr">
@@ -20907,7 +20615,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P297" t="inlineStr"/>
     </row>
     <row r="298" ht="28" customHeight="1" s="84">
       <c r="A298" t="inlineStr">
@@ -20975,7 +20682,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P298" t="inlineStr"/>
     </row>
     <row r="299" ht="28" customHeight="1" s="84">
       <c r="A299" t="inlineStr">
@@ -21043,7 +20749,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P299" t="inlineStr"/>
     </row>
     <row r="300" ht="28" customHeight="1" s="84">
       <c r="A300" t="inlineStr">
@@ -21111,7 +20816,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P300" t="inlineStr"/>
     </row>
     <row r="301" ht="28" customHeight="1" s="84">
       <c r="A301" t="inlineStr">
@@ -21179,7 +20883,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P301" t="inlineStr"/>
     </row>
     <row r="302" ht="28" customHeight="1" s="84">
       <c r="A302" t="inlineStr">
@@ -21247,7 +20950,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P302" t="inlineStr"/>
     </row>
     <row r="303" ht="28" customHeight="1" s="84">
       <c r="A303" t="inlineStr">
@@ -21315,7 +21017,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P303" t="inlineStr"/>
     </row>
     <row r="304" ht="28" customHeight="1" s="84">
       <c r="A304" t="inlineStr">
@@ -21383,7 +21084,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P304" t="inlineStr"/>
     </row>
     <row r="305" ht="28" customHeight="1" s="84">
       <c r="A305" t="inlineStr">
@@ -21451,7 +21151,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P305" t="inlineStr"/>
     </row>
     <row r="306" ht="28" customHeight="1" s="84">
       <c r="A306" t="inlineStr">
@@ -21519,7 +21218,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P306" t="inlineStr"/>
     </row>
     <row r="307" ht="28" customHeight="1" s="84">
       <c r="A307" t="inlineStr">
@@ -21587,7 +21285,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P307" t="inlineStr"/>
     </row>
     <row r="308" ht="28" customHeight="1" s="84">
       <c r="A308" t="inlineStr">
@@ -21655,7 +21352,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P308" t="inlineStr"/>
     </row>
     <row r="309" ht="28" customHeight="1" s="84">
       <c r="A309" t="inlineStr">
@@ -21723,7 +21419,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P309" t="inlineStr"/>
     </row>
     <row r="310" ht="28" customHeight="1" s="84">
       <c r="A310" t="inlineStr">
@@ -21791,7 +21486,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P310" t="inlineStr"/>
     </row>
     <row r="311" ht="28" customHeight="1" s="84">
       <c r="A311" t="inlineStr">
@@ -21859,7 +21553,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P311" t="inlineStr"/>
     </row>
     <row r="312" ht="28" customHeight="1" s="84">
       <c r="A312" t="inlineStr">
@@ -21927,7 +21620,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P312" t="inlineStr"/>
     </row>
     <row r="313" ht="28" customHeight="1" s="84">
       <c r="A313" t="inlineStr">
@@ -21995,7 +21687,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P313" t="inlineStr"/>
     </row>
     <row r="314" ht="28" customHeight="1" s="84">
       <c r="A314" t="inlineStr">
@@ -22063,7 +21754,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P314" t="inlineStr"/>
     </row>
     <row r="315" ht="28" customHeight="1" s="84">
       <c r="A315" t="inlineStr">
@@ -22131,7 +21821,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P315" t="inlineStr"/>
     </row>
     <row r="316" ht="28" customHeight="1" s="84">
       <c r="A316" t="inlineStr">
@@ -22199,7 +21888,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P316" t="inlineStr"/>
     </row>
     <row r="317" ht="28" customHeight="1" s="84">
       <c r="A317" t="inlineStr">
@@ -22267,7 +21955,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P317" t="inlineStr"/>
     </row>
     <row r="318" ht="28" customHeight="1" s="84">
       <c r="A318" t="inlineStr">
@@ -22335,7 +22022,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P318" t="inlineStr"/>
     </row>
     <row r="319" ht="28" customHeight="1" s="84">
       <c r="A319" t="inlineStr">
@@ -22403,7 +22089,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P319" t="inlineStr"/>
     </row>
     <row r="320" ht="28" customHeight="1" s="84">
       <c r="A320" t="inlineStr">
@@ -22471,7 +22156,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P320" t="inlineStr"/>
     </row>
     <row r="321" ht="28" customHeight="1" s="84">
       <c r="A321" t="inlineStr">
@@ -22539,7 +22223,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P321" t="inlineStr"/>
     </row>
     <row r="322" ht="28" customHeight="1" s="84">
       <c r="A322" t="inlineStr">
@@ -22607,7 +22290,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P322" t="inlineStr"/>
     </row>
     <row r="323" ht="28" customHeight="1" s="84">
       <c r="A323" t="inlineStr">
@@ -22675,7 +22357,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P323" t="inlineStr"/>
     </row>
     <row r="324" ht="28" customHeight="1" s="84">
       <c r="A324" t="inlineStr">
@@ -22743,7 +22424,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P324" t="inlineStr"/>
     </row>
     <row r="325" ht="28" customHeight="1" s="84">
       <c r="A325" t="inlineStr">
@@ -22811,7 +22491,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P325" t="inlineStr"/>
     </row>
     <row r="326" ht="28" customHeight="1" s="84">
       <c r="A326" t="inlineStr">
@@ -22879,7 +22558,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P326" t="inlineStr"/>
     </row>
     <row r="327" ht="28" customHeight="1" s="84">
       <c r="A327" t="inlineStr">
@@ -22947,7 +22625,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P327" t="inlineStr"/>
     </row>
     <row r="328" ht="28" customHeight="1" s="84">
       <c r="A328" t="inlineStr">
@@ -23015,7 +22692,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P328" t="inlineStr"/>
     </row>
     <row r="329" ht="28" customHeight="1" s="84">
       <c r="A329" t="inlineStr">
@@ -23083,7 +22759,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P329" t="inlineStr"/>
     </row>
     <row r="330" ht="28" customHeight="1" s="84">
       <c r="A330" t="inlineStr">
@@ -23151,7 +22826,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P330" t="inlineStr"/>
     </row>
     <row r="331" ht="28" customHeight="1" s="84">
       <c r="A331" t="inlineStr">
@@ -23219,7 +22893,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P331" t="inlineStr"/>
     </row>
     <row r="332" ht="28" customHeight="1" s="84">
       <c r="A332" t="inlineStr">
@@ -23287,7 +22960,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P332" t="inlineStr"/>
     </row>
     <row r="333" ht="28" customHeight="1" s="84">
       <c r="A333" t="inlineStr">
@@ -23355,7 +23027,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P333" t="inlineStr"/>
     </row>
     <row r="334" ht="28" customHeight="1" s="84">
       <c r="A334" t="inlineStr">
@@ -23423,7 +23094,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P334" t="inlineStr"/>
     </row>
     <row r="335" ht="28" customHeight="1" s="84">
       <c r="A335" t="inlineStr">
@@ -23491,7 +23161,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P335" t="inlineStr"/>
     </row>
     <row r="336" ht="28" customHeight="1" s="84">
       <c r="A336" t="inlineStr">
@@ -23559,7 +23228,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P336" t="inlineStr"/>
     </row>
     <row r="337" ht="28" customHeight="1" s="84">
       <c r="A337" t="inlineStr">
@@ -23627,7 +23295,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P337" t="inlineStr"/>
     </row>
     <row r="338" ht="28" customHeight="1" s="84">
       <c r="A338" t="inlineStr">
@@ -23695,7 +23362,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P338" t="inlineStr"/>
     </row>
     <row r="339" ht="28" customHeight="1" s="84">
       <c r="A339" t="inlineStr">
@@ -23763,7 +23429,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P339" t="inlineStr"/>
     </row>
     <row r="340" ht="28" customHeight="1" s="84">
       <c r="A340" t="inlineStr">
@@ -23831,7 +23496,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P340" t="inlineStr"/>
     </row>
     <row r="341" ht="28" customHeight="1" s="84">
       <c r="A341" t="inlineStr">
@@ -23899,7 +23563,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P341" t="inlineStr"/>
     </row>
     <row r="342" ht="28" customHeight="1" s="84">
       <c r="A342" t="inlineStr">
@@ -23967,7 +23630,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P342" t="inlineStr"/>
     </row>
     <row r="343" ht="28" customHeight="1" s="84">
       <c r="A343" t="inlineStr">
@@ -24035,7 +23697,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P343" t="inlineStr"/>
     </row>
     <row r="344" ht="28" customHeight="1" s="84">
       <c r="A344" t="inlineStr">
@@ -24103,7 +23764,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P344" t="inlineStr"/>
     </row>
     <row r="345" ht="28" customHeight="1" s="84">
       <c r="A345" t="inlineStr">
@@ -24171,7 +23831,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P345" t="inlineStr"/>
     </row>
     <row r="346" ht="28" customHeight="1" s="84">
       <c r="A346" t="inlineStr">
@@ -24239,7 +23898,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P346" t="inlineStr"/>
     </row>
     <row r="347" ht="28" customHeight="1" s="84">
       <c r="A347" t="inlineStr">
@@ -24307,7 +23965,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P347" t="inlineStr"/>
     </row>
     <row r="348" ht="28" customHeight="1" s="84">
       <c r="A348" t="inlineStr">
@@ -24375,7 +24032,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P348" t="inlineStr"/>
     </row>
     <row r="349" ht="28" customHeight="1" s="84">
       <c r="A349" t="inlineStr">
@@ -24443,7 +24099,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P349" t="inlineStr"/>
     </row>
     <row r="350" ht="28" customHeight="1" s="84">
       <c r="A350" t="inlineStr">
@@ -24511,7 +24166,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P350" t="inlineStr"/>
     </row>
     <row r="351" ht="28" customHeight="1" s="84">
       <c r="A351" t="inlineStr">
@@ -24579,7 +24233,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P351" t="inlineStr"/>
     </row>
     <row r="352" ht="28" customHeight="1" s="84">
       <c r="A352" t="inlineStr">
@@ -24647,7 +24300,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P352" t="inlineStr"/>
     </row>
     <row r="353" ht="28" customHeight="1" s="84">
       <c r="A353" t="inlineStr">
@@ -24715,7 +24367,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P353" t="inlineStr"/>
     </row>
     <row r="354" ht="28" customHeight="1" s="84">
       <c r="A354" t="inlineStr">
@@ -24783,7 +24434,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P354" t="inlineStr"/>
     </row>
     <row r="355" ht="28" customHeight="1" s="84">
       <c r="A355" t="inlineStr">
@@ -24851,7 +24501,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P355" t="inlineStr"/>
     </row>
     <row r="356" ht="28" customHeight="1" s="84">
       <c r="A356" t="inlineStr">
@@ -24919,7 +24568,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P356" t="inlineStr"/>
     </row>
     <row r="357" ht="28" customHeight="1" s="84">
       <c r="A357" t="inlineStr">
@@ -24987,7 +24635,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P357" t="inlineStr"/>
     </row>
     <row r="358" ht="28" customHeight="1" s="84">
       <c r="A358" t="inlineStr">
@@ -25055,7 +24702,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P358" t="inlineStr"/>
     </row>
     <row r="359" ht="28" customHeight="1" s="84">
       <c r="A359" t="inlineStr">
@@ -25123,7 +24769,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P359" t="inlineStr"/>
     </row>
     <row r="360" ht="28" customHeight="1" s="84">
       <c r="A360" t="inlineStr">
@@ -25191,7 +24836,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P360" t="inlineStr"/>
     </row>
     <row r="361" ht="28" customHeight="1" s="84">
       <c r="A361" t="inlineStr">
@@ -25259,7 +24903,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P361" t="inlineStr"/>
     </row>
     <row r="362" ht="28" customHeight="1" s="84">
       <c r="A362" t="inlineStr">
@@ -25327,7 +24970,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P362" t="inlineStr"/>
     </row>
     <row r="363" ht="28" customHeight="1" s="84">
       <c r="A363" t="inlineStr">
@@ -25395,7 +25037,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P363" t="inlineStr"/>
     </row>
     <row r="364" ht="28" customHeight="1" s="84">
       <c r="A364" t="inlineStr">
@@ -25463,7 +25104,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P364" t="inlineStr"/>
     </row>
     <row r="365" ht="28" customHeight="1" s="84">
       <c r="A365" t="inlineStr">
@@ -25531,7 +25171,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P365" t="inlineStr"/>
     </row>
     <row r="366" ht="28" customHeight="1" s="84">
       <c r="A366" t="inlineStr">
@@ -25599,7 +25238,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P366" t="inlineStr"/>
     </row>
     <row r="367" ht="28" customHeight="1" s="84">
       <c r="A367" t="inlineStr">
@@ -25667,7 +25305,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P367" t="inlineStr"/>
     </row>
     <row r="368" ht="28" customHeight="1" s="84">
       <c r="A368" t="inlineStr">
@@ -25735,7 +25372,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P368" t="inlineStr"/>
     </row>
     <row r="369" ht="28" customHeight="1" s="84">
       <c r="A369" t="inlineStr">
@@ -25803,7 +25439,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P369" t="inlineStr"/>
     </row>
     <row r="370" ht="28" customHeight="1" s="84">
       <c r="A370" t="inlineStr">
@@ -25871,7 +25506,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P370" t="inlineStr"/>
     </row>
     <row r="371" ht="28" customHeight="1" s="84">
       <c r="A371" t="inlineStr">
@@ -25939,7 +25573,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P371" t="inlineStr"/>
     </row>
     <row r="372" ht="28" customHeight="1" s="84">
       <c r="A372" t="inlineStr">
@@ -26007,7 +25640,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P372" t="inlineStr"/>
     </row>
     <row r="373" ht="28" customHeight="1" s="84">
       <c r="A373" t="inlineStr">
@@ -26075,7 +25707,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P373" t="inlineStr"/>
     </row>
     <row r="374" ht="28" customHeight="1" s="84">
       <c r="A374" t="inlineStr">
@@ -26143,7 +25774,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P374" t="inlineStr"/>
     </row>
     <row r="375" ht="28" customHeight="1" s="84">
       <c r="A375" t="inlineStr">
@@ -26211,7 +25841,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P375" t="inlineStr"/>
     </row>
     <row r="376" ht="28" customHeight="1" s="84">
       <c r="A376" t="inlineStr">
@@ -26279,7 +25908,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P376" t="inlineStr"/>
     </row>
     <row r="377" ht="28" customHeight="1" s="84">
       <c r="A377" t="inlineStr">
@@ -26347,7 +25975,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P377" t="inlineStr"/>
     </row>
     <row r="378" ht="28" customHeight="1" s="84">
       <c r="A378" t="inlineStr">
@@ -26415,7 +26042,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P378" t="inlineStr"/>
     </row>
     <row r="379" ht="28" customHeight="1" s="84">
       <c r="A379" t="inlineStr">
@@ -26483,7 +26109,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P379" t="inlineStr"/>
     </row>
     <row r="380" ht="28" customHeight="1" s="84">
       <c r="A380" t="inlineStr">
@@ -26551,7 +26176,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P380" t="inlineStr"/>
     </row>
     <row r="381" ht="28" customHeight="1" s="84">
       <c r="A381" t="inlineStr">
@@ -26619,7 +26243,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P381" t="inlineStr"/>
     </row>
     <row r="382" ht="28" customHeight="1" s="84">
       <c r="A382" t="inlineStr">
@@ -26687,7 +26310,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P382" t="inlineStr"/>
     </row>
     <row r="383" ht="28" customHeight="1" s="84">
       <c r="A383" t="inlineStr">
@@ -26755,7 +26377,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P383" t="inlineStr"/>
     </row>
     <row r="384" ht="28" customHeight="1" s="84">
       <c r="A384" t="inlineStr">
@@ -26823,7 +26444,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P384" t="inlineStr"/>
     </row>
     <row r="385" ht="28" customHeight="1" s="84">
       <c r="A385" t="inlineStr">
@@ -26891,7 +26511,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P385" t="inlineStr"/>
     </row>
     <row r="386" ht="28" customHeight="1" s="84">
       <c r="A386" t="inlineStr">
@@ -26959,7 +26578,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P386" t="inlineStr"/>
     </row>
     <row r="387" ht="28" customHeight="1" s="84">
       <c r="A387" t="inlineStr">
@@ -27027,7 +26645,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P387" t="inlineStr"/>
     </row>
     <row r="388" ht="28" customHeight="1" s="84">
       <c r="A388" t="inlineStr">
@@ -27095,7 +26712,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P388" t="inlineStr"/>
     </row>
     <row r="389" ht="28" customHeight="1" s="84">
       <c r="A389" t="inlineStr">
@@ -27163,7 +26779,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P389" t="inlineStr"/>
     </row>
     <row r="390" ht="28" customHeight="1" s="84">
       <c r="A390" t="inlineStr">
@@ -27231,7 +26846,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P390" t="inlineStr"/>
     </row>
     <row r="391" ht="28" customHeight="1" s="84">
       <c r="A391" t="inlineStr">
@@ -27299,7 +26913,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P391" t="inlineStr"/>
     </row>
     <row r="392" ht="28" customHeight="1" s="84">
       <c r="A392" t="inlineStr">
@@ -27367,7 +26980,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P392" t="inlineStr"/>
     </row>
     <row r="393" ht="28" customHeight="1" s="84">
       <c r="A393" t="inlineStr">
@@ -27435,7 +27047,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P393" t="inlineStr"/>
     </row>
     <row r="394" ht="28" customHeight="1" s="84">
       <c r="A394" t="inlineStr">
@@ -27503,7 +27114,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P394" t="inlineStr"/>
     </row>
     <row r="395" ht="28" customHeight="1" s="84">
       <c r="A395" t="inlineStr">
@@ -27571,7 +27181,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P395" t="inlineStr"/>
     </row>
     <row r="396" ht="28" customHeight="1" s="84">
       <c r="A396" t="inlineStr">
@@ -27639,7 +27248,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P396" t="inlineStr"/>
     </row>
     <row r="397" ht="28" customHeight="1" s="84">
       <c r="A397" t="inlineStr">
@@ -27707,7 +27315,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P397" t="inlineStr"/>
     </row>
     <row r="398" ht="28" customHeight="1" s="84">
       <c r="A398" t="inlineStr">
@@ -27775,7 +27382,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P398" t="inlineStr"/>
     </row>
     <row r="399" ht="28" customHeight="1" s="84">
       <c r="A399" t="inlineStr">
@@ -27843,7 +27449,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P399" t="inlineStr"/>
     </row>
     <row r="400" ht="28" customHeight="1" s="84">
       <c r="A400" t="inlineStr">
@@ -27911,7 +27516,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P400" t="inlineStr"/>
     </row>
     <row r="401" ht="28" customHeight="1" s="84">
       <c r="A401" t="inlineStr">
@@ -27979,7 +27583,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P401" t="inlineStr"/>
     </row>
     <row r="402" ht="28" customHeight="1" s="84">
       <c r="A402" t="inlineStr">
@@ -28047,7 +27650,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P402" t="inlineStr"/>
     </row>
     <row r="403" ht="28" customHeight="1" s="84">
       <c r="A403" t="inlineStr">
@@ -28115,7 +27717,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P403" t="inlineStr"/>
     </row>
     <row r="404" ht="28" customHeight="1" s="84">
       <c r="A404" t="inlineStr">
@@ -28183,7 +27784,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P404" t="inlineStr"/>
     </row>
     <row r="405" ht="28" customHeight="1" s="84">
       <c r="A405" t="inlineStr">
@@ -28251,7 +27851,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P405" t="inlineStr"/>
     </row>
     <row r="406" ht="28" customHeight="1" s="84">
       <c r="A406" t="inlineStr">
@@ -28319,7 +27918,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P406" t="inlineStr"/>
     </row>
     <row r="407" ht="28" customHeight="1" s="84">
       <c r="A407" t="inlineStr">
@@ -28387,7 +27985,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P407" t="inlineStr"/>
     </row>
     <row r="408" ht="28" customHeight="1" s="84">
       <c r="A408" t="inlineStr">
@@ -28455,7 +28052,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P408" t="inlineStr"/>
     </row>
     <row r="409" ht="28" customHeight="1" s="84">
       <c r="A409" t="inlineStr">
@@ -28523,7 +28119,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P409" t="inlineStr"/>
     </row>
     <row r="410" ht="28" customHeight="1" s="84">
       <c r="A410" t="inlineStr">
@@ -28591,7 +28186,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P410" t="inlineStr"/>
     </row>
     <row r="411" ht="28" customHeight="1" s="84">
       <c r="A411" t="inlineStr">
@@ -28659,7 +28253,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P411" t="inlineStr"/>
     </row>
     <row r="412" ht="28" customHeight="1" s="84">
       <c r="A412" t="inlineStr">
@@ -28727,7 +28320,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P412" t="inlineStr"/>
     </row>
     <row r="413" ht="28" customHeight="1" s="84">
       <c r="A413" t="inlineStr">
@@ -28795,7 +28387,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P413" t="inlineStr"/>
     </row>
     <row r="414" ht="28" customHeight="1" s="84">
       <c r="A414" t="inlineStr">
@@ -28863,7 +28454,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P414" t="inlineStr"/>
     </row>
     <row r="415" ht="28" customHeight="1" s="84">
       <c r="A415" t="inlineStr">
@@ -28931,7 +28521,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P415" t="inlineStr"/>
     </row>
     <row r="416" ht="28" customHeight="1" s="84">
       <c r="A416" t="inlineStr">
@@ -28999,7 +28588,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P416" t="inlineStr"/>
     </row>
     <row r="417" ht="28" customHeight="1" s="84">
       <c r="A417" t="inlineStr">
@@ -29067,7 +28655,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P417" t="inlineStr"/>
     </row>
     <row r="418" ht="28" customHeight="1" s="84">
       <c r="A418" t="inlineStr">
@@ -29135,7 +28722,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P418" t="inlineStr"/>
     </row>
     <row r="419" ht="28" customHeight="1" s="84">
       <c r="A419" t="inlineStr">
@@ -29203,7 +28789,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P419" t="inlineStr"/>
     </row>
     <row r="420" ht="28" customHeight="1" s="84">
       <c r="A420" t="inlineStr">
@@ -29271,7 +28856,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P420" t="inlineStr"/>
     </row>
     <row r="421" ht="28" customHeight="1" s="84">
       <c r="A421" t="inlineStr">
@@ -29339,7 +28923,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P421" t="inlineStr"/>
     </row>
     <row r="422" ht="28" customHeight="1" s="84">
       <c r="A422" t="inlineStr">
@@ -29407,7 +28990,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P422" t="inlineStr"/>
     </row>
     <row r="423" ht="28" customHeight="1" s="84">
       <c r="A423" t="inlineStr">
@@ -29475,7 +29057,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P423" t="inlineStr"/>
     </row>
     <row r="424" ht="28" customHeight="1" s="84">
       <c r="A424" t="inlineStr">
@@ -29543,7 +29124,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P424" t="inlineStr"/>
     </row>
     <row r="425" ht="28" customHeight="1" s="84">
       <c r="A425" t="inlineStr">
@@ -29611,7 +29191,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P425" t="inlineStr"/>
     </row>
     <row r="426" ht="28" customHeight="1" s="84">
       <c r="A426" t="inlineStr">
@@ -29679,7 +29258,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P426" t="inlineStr"/>
     </row>
     <row r="427" ht="28" customHeight="1" s="84">
       <c r="A427" t="inlineStr">
@@ -29747,7 +29325,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P427" t="inlineStr"/>
     </row>
     <row r="428" ht="28" customHeight="1" s="84">
       <c r="A428" t="inlineStr">
@@ -29815,7 +29392,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P428" t="inlineStr"/>
     </row>
     <row r="429" ht="28" customHeight="1" s="84">
       <c r="A429" t="inlineStr">
@@ -29883,7 +29459,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P429" t="inlineStr"/>
     </row>
     <row r="430" ht="28" customHeight="1" s="84">
       <c r="A430" t="inlineStr">
@@ -29951,7 +29526,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P430" t="inlineStr"/>
     </row>
     <row r="431" ht="28" customHeight="1" s="84">
       <c r="A431" t="inlineStr">
@@ -30019,7 +29593,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P431" t="inlineStr"/>
     </row>
     <row r="432" ht="28" customHeight="1" s="84">
       <c r="A432" t="inlineStr">
@@ -30087,7 +29660,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P432" t="inlineStr"/>
     </row>
     <row r="433" ht="28" customHeight="1" s="84">
       <c r="A433" t="inlineStr">
@@ -30155,7 +29727,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P433" t="inlineStr"/>
     </row>
     <row r="434" ht="28" customHeight="1" s="84">
       <c r="A434" t="inlineStr">
@@ -30223,7 +29794,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P434" t="inlineStr"/>
     </row>
     <row r="435" ht="28" customHeight="1" s="84">
       <c r="A435" t="inlineStr">
@@ -30291,7 +29861,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P435" t="inlineStr"/>
     </row>
     <row r="436" ht="28" customHeight="1" s="84">
       <c r="A436" t="inlineStr">
@@ -30359,7 +29928,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P436" t="inlineStr"/>
     </row>
     <row r="437" ht="28" customHeight="1" s="84">
       <c r="A437" t="inlineStr">
@@ -30427,7 +29995,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P437" t="inlineStr"/>
     </row>
     <row r="438" ht="28" customHeight="1" s="84">
       <c r="A438" t="inlineStr">
@@ -30495,7 +30062,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P438" t="inlineStr"/>
     </row>
     <row r="439" ht="28" customHeight="1" s="84">
       <c r="A439" t="inlineStr">
@@ -30563,7 +30129,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P439" t="inlineStr"/>
     </row>
     <row r="440" ht="28" customHeight="1" s="84">
       <c r="A440" t="inlineStr">
@@ -30631,7 +30196,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P440" t="inlineStr"/>
     </row>
     <row r="441" ht="28" customHeight="1" s="84">
       <c r="A441" t="inlineStr">
@@ -30699,7 +30263,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P441" t="inlineStr"/>
     </row>
     <row r="442" ht="28" customHeight="1" s="84">
       <c r="A442" t="inlineStr">
@@ -30767,7 +30330,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P442" t="inlineStr"/>
     </row>
     <row r="443" ht="28" customHeight="1" s="84">
       <c r="A443" t="inlineStr">
@@ -30835,7 +30397,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P443" t="inlineStr"/>
     </row>
     <row r="444" ht="28" customHeight="1" s="84">
       <c r="A444" t="inlineStr">
@@ -30903,7 +30464,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P444" t="inlineStr"/>
     </row>
     <row r="445" ht="28" customHeight="1" s="84">
       <c r="A445" t="inlineStr">
@@ -30971,7 +30531,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P445" t="inlineStr"/>
     </row>
     <row r="446" ht="28" customHeight="1" s="84">
       <c r="A446" t="inlineStr">
@@ -31039,7 +30598,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P446" t="inlineStr"/>
     </row>
     <row r="447" ht="28" customHeight="1" s="84">
       <c r="A447" t="inlineStr">
@@ -31107,7 +30665,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P447" t="inlineStr"/>
     </row>
     <row r="448" ht="28" customHeight="1" s="84">
       <c r="A448" t="inlineStr">
@@ -31175,7 +30732,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P448" t="inlineStr"/>
     </row>
     <row r="449" ht="28" customHeight="1" s="84">
       <c r="A449" t="inlineStr">
@@ -31243,7 +30799,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P449" t="inlineStr"/>
     </row>
     <row r="450" ht="28" customHeight="1" s="84">
       <c r="A450" t="inlineStr">
@@ -31311,7 +30866,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P450" t="inlineStr"/>
     </row>
     <row r="451" ht="28" customHeight="1" s="84">
       <c r="A451" t="inlineStr">
@@ -31379,7 +30933,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P451" t="inlineStr"/>
     </row>
     <row r="452" ht="28" customHeight="1" s="84">
       <c r="A452" t="inlineStr">
@@ -31447,7 +31000,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P452" t="inlineStr"/>
     </row>
     <row r="453" ht="28" customHeight="1" s="84">
       <c r="A453" t="inlineStr">
@@ -31515,7 +31067,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P453" t="inlineStr"/>
     </row>
     <row r="454" ht="28" customHeight="1" s="84">
       <c r="A454" t="inlineStr">
@@ -31583,7 +31134,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P454" t="inlineStr"/>
     </row>
     <row r="455" ht="28" customHeight="1" s="84">
       <c r="A455" t="inlineStr">
@@ -31651,7 +31201,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P455" t="inlineStr"/>
     </row>
     <row r="456" ht="28" customHeight="1" s="84">
       <c r="A456" t="inlineStr">
@@ -31719,7 +31268,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P456" t="inlineStr"/>
     </row>
     <row r="457" ht="28" customHeight="1" s="84">
       <c r="A457" t="inlineStr">
@@ -31787,7 +31335,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P457" t="inlineStr"/>
     </row>
     <row r="458" ht="28" customHeight="1" s="84">
       <c r="A458" t="inlineStr">
@@ -31855,7 +31402,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P458" t="inlineStr"/>
     </row>
     <row r="459" ht="28" customHeight="1" s="84">
       <c r="A459" t="inlineStr">
@@ -31923,7 +31469,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P459" t="inlineStr"/>
     </row>
     <row r="460" ht="28" customHeight="1" s="84">
       <c r="A460" t="inlineStr">
@@ -31991,7 +31536,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P460" t="inlineStr"/>
     </row>
     <row r="461" ht="28" customHeight="1" s="84">
       <c r="A461" t="inlineStr">
@@ -32059,7 +31603,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P461" t="inlineStr"/>
     </row>
     <row r="462" ht="28" customHeight="1" s="84">
       <c r="A462" t="inlineStr">
@@ -32127,7 +31670,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P462" t="inlineStr"/>
     </row>
     <row r="463" ht="28" customHeight="1" s="84">
       <c r="A463" t="inlineStr">
@@ -32195,7 +31737,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P463" t="inlineStr"/>
     </row>
     <row r="464" ht="28" customHeight="1" s="84">
       <c r="A464" t="inlineStr">
@@ -32263,7 +31804,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P464" t="inlineStr"/>
     </row>
     <row r="465" ht="28" customHeight="1" s="84">
       <c r="A465" t="inlineStr">
@@ -32331,7 +31871,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P465" t="inlineStr"/>
     </row>
     <row r="466" ht="28" customHeight="1" s="84">
       <c r="A466" t="inlineStr">
@@ -32399,7 +31938,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P466" t="inlineStr"/>
     </row>
     <row r="467" ht="28" customHeight="1" s="84">
       <c r="A467" t="inlineStr">
@@ -32467,7 +32005,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P467" t="inlineStr"/>
     </row>
     <row r="468" ht="28" customHeight="1" s="84">
       <c r="A468" t="inlineStr">
@@ -32535,7 +32072,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P468" t="inlineStr"/>
     </row>
     <row r="469" ht="28" customHeight="1" s="84">
       <c r="A469" t="inlineStr">
@@ -32603,7 +32139,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P469" t="inlineStr"/>
     </row>
     <row r="470" ht="28" customHeight="1" s="84">
       <c r="A470" t="inlineStr">
@@ -32671,7 +32206,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P470" t="inlineStr"/>
     </row>
     <row r="471" ht="28" customHeight="1" s="84">
       <c r="A471" t="inlineStr">
@@ -32739,7 +32273,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P471" t="inlineStr"/>
     </row>
     <row r="472" ht="28" customHeight="1" s="84">
       <c r="A472" t="inlineStr">
@@ -32807,7 +32340,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P472" t="inlineStr"/>
     </row>
     <row r="473" ht="28" customHeight="1" s="84">
       <c r="A473" t="inlineStr">
@@ -32875,7 +32407,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P473" t="inlineStr"/>
     </row>
     <row r="474" ht="28" customHeight="1" s="84">
       <c r="A474" t="inlineStr">
@@ -32943,7 +32474,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P474" t="inlineStr"/>
     </row>
     <row r="475" ht="28" customHeight="1" s="84">
       <c r="A475" t="inlineStr">
@@ -33011,7 +32541,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P475" t="inlineStr"/>
     </row>
     <row r="476" ht="28" customHeight="1" s="84">
       <c r="A476" t="inlineStr">
@@ -33079,7 +32608,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P476" t="inlineStr"/>
     </row>
     <row r="477" ht="28" customHeight="1" s="84">
       <c r="A477" t="inlineStr">
@@ -33147,7 +32675,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P477" t="inlineStr"/>
     </row>
     <row r="478" ht="28" customHeight="1" s="84">
       <c r="A478" t="inlineStr">
@@ -33215,7 +32742,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P478" t="inlineStr"/>
     </row>
     <row r="479" ht="28" customHeight="1" s="84">
       <c r="A479" t="inlineStr">
@@ -33283,7 +32809,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P479" t="inlineStr"/>
     </row>
     <row r="480" ht="28" customHeight="1" s="84">
       <c r="A480" t="inlineStr">
@@ -33351,7 +32876,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P480" t="inlineStr"/>
     </row>
     <row r="481" ht="28" customHeight="1" s="84">
       <c r="A481" t="inlineStr">
@@ -33419,7 +32943,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P481" t="inlineStr"/>
     </row>
     <row r="482" ht="28" customHeight="1" s="84">
       <c r="A482" t="inlineStr">
@@ -33487,7 +33010,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P482" t="inlineStr"/>
     </row>
     <row r="483" ht="28" customHeight="1" s="84">
       <c r="A483" t="inlineStr">
@@ -33555,7 +33077,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P483" t="inlineStr"/>
     </row>
     <row r="484" ht="28" customHeight="1" s="84">
       <c r="A484" t="inlineStr">
@@ -33623,7 +33144,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P484" t="inlineStr"/>
     </row>
     <row r="485" ht="28" customHeight="1" s="84">
       <c r="A485" t="inlineStr">
@@ -33691,7 +33211,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P485" t="inlineStr"/>
     </row>
     <row r="486" ht="28" customHeight="1" s="84">
       <c r="A486" t="inlineStr">
@@ -33759,7 +33278,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P486" t="inlineStr"/>
     </row>
     <row r="487" ht="28" customHeight="1" s="84">
       <c r="A487" t="inlineStr">
@@ -33827,7 +33345,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P487" t="inlineStr"/>
     </row>
     <row r="488" ht="28" customHeight="1" s="84">
       <c r="A488" t="inlineStr">
@@ -33895,7 +33412,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P488" t="inlineStr"/>
     </row>
     <row r="489" ht="28" customHeight="1" s="84">
       <c r="A489" t="inlineStr">
@@ -33963,7 +33479,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P489" t="inlineStr"/>
     </row>
     <row r="490" ht="28" customHeight="1" s="84">
       <c r="A490" t="inlineStr">
@@ -34031,7 +33546,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P490" t="inlineStr"/>
     </row>
     <row r="491" ht="28" customHeight="1" s="84">
       <c r="A491" t="inlineStr">
@@ -34099,7 +33613,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P491" t="inlineStr"/>
     </row>
     <row r="492" ht="28" customHeight="1" s="84">
       <c r="A492" t="inlineStr">
@@ -34167,7 +33680,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P492" t="inlineStr"/>
     </row>
     <row r="493" ht="28" customHeight="1" s="84">
       <c r="A493" t="inlineStr">
@@ -34235,7 +33747,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P493" t="inlineStr"/>
     </row>
     <row r="494" ht="28" customHeight="1" s="84">
       <c r="A494" t="inlineStr">
@@ -34303,7 +33814,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P494" t="inlineStr"/>
     </row>
     <row r="495" ht="28" customHeight="1" s="84">
       <c r="A495" t="inlineStr">
@@ -34371,7 +33881,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P495" t="inlineStr"/>
     </row>
     <row r="496" ht="28" customHeight="1" s="84">
       <c r="A496" t="inlineStr">
@@ -34439,7 +33948,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P496" t="inlineStr"/>
     </row>
     <row r="497" ht="28" customHeight="1" s="84">
       <c r="A497" t="inlineStr">
@@ -34507,7 +34015,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P497" t="inlineStr"/>
     </row>
     <row r="498" ht="28" customHeight="1" s="84">
       <c r="A498" t="inlineStr">
@@ -34575,7 +34082,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P498" t="inlineStr"/>
     </row>
     <row r="499" ht="28" customHeight="1" s="84">
       <c r="A499" t="inlineStr">
@@ -34643,7 +34149,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P499" t="inlineStr"/>
     </row>
     <row r="500" ht="28" customHeight="1" s="84">
       <c r="A500" t="inlineStr">
@@ -34711,7 +34216,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P500" t="inlineStr"/>
     </row>
     <row r="501" ht="28" customHeight="1" s="84">
       <c r="A501" t="inlineStr">
@@ -34779,7 +34283,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P501" t="inlineStr"/>
     </row>
     <row r="502" ht="28" customHeight="1" s="84">
       <c r="A502" t="inlineStr">
@@ -34847,7 +34350,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P502" t="inlineStr"/>
     </row>
     <row r="503" ht="28" customHeight="1" s="84">
       <c r="A503" t="inlineStr">
@@ -34915,7 +34417,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P503" t="inlineStr"/>
     </row>
     <row r="504" ht="28" customHeight="1" s="84">
       <c r="A504" t="inlineStr">
@@ -34983,7 +34484,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P504" t="inlineStr"/>
     </row>
     <row r="505" ht="28" customHeight="1" s="84">
       <c r="A505" t="inlineStr">
@@ -35051,7 +34551,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P505" t="inlineStr"/>
     </row>
     <row r="506" ht="28" customHeight="1" s="84">
       <c r="A506" t="inlineStr">
@@ -35119,7 +34618,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P506" t="inlineStr"/>
     </row>
     <row r="507" ht="28" customHeight="1" s="84">
       <c r="A507" t="inlineStr">
@@ -35187,7 +34685,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P507" t="inlineStr"/>
     </row>
     <row r="508" ht="28" customHeight="1" s="84">
       <c r="A508" t="inlineStr">
@@ -35255,7 +34752,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P508" t="inlineStr"/>
     </row>
     <row r="509" ht="28" customHeight="1" s="84">
       <c r="A509" t="inlineStr">
@@ -35323,7 +34819,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P509" t="inlineStr"/>
     </row>
     <row r="510" ht="28" customHeight="1" s="84">
       <c r="A510" t="inlineStr">
@@ -35391,7 +34886,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P510" t="inlineStr"/>
     </row>
     <row r="511" ht="28" customHeight="1" s="84">
       <c r="A511" t="inlineStr">
@@ -35459,7 +34953,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P511" t="inlineStr"/>
     </row>
     <row r="512" ht="28" customHeight="1" s="84">
       <c r="A512" t="inlineStr">
@@ -35527,7 +35020,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P512" t="inlineStr"/>
     </row>
     <row r="513" ht="28" customHeight="1" s="84">
       <c r="A513" t="inlineStr">
@@ -35595,7 +35087,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P513" t="inlineStr"/>
     </row>
     <row r="514" ht="28" customHeight="1" s="84">
       <c r="A514" t="inlineStr">
@@ -35663,7 +35154,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P514" t="inlineStr"/>
     </row>
     <row r="515" ht="28" customHeight="1" s="84">
       <c r="A515" t="inlineStr">
@@ -35731,7 +35221,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P515" t="inlineStr"/>
     </row>
     <row r="516" ht="28" customHeight="1" s="84">
       <c r="A516" t="inlineStr">
@@ -35799,7 +35288,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P516" t="inlineStr"/>
     </row>
     <row r="517" ht="28" customHeight="1" s="84">
       <c r="A517" t="inlineStr">
@@ -35867,7 +35355,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P517" t="inlineStr"/>
     </row>
     <row r="518" ht="28" customHeight="1" s="84">
       <c r="A518" t="inlineStr">
@@ -35935,7 +35422,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P518" t="inlineStr"/>
     </row>
     <row r="519" ht="28" customHeight="1" s="84">
       <c r="A519" t="inlineStr">
@@ -36003,7 +35489,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P519" t="inlineStr"/>
     </row>
     <row r="520" ht="28" customHeight="1" s="84">
       <c r="A520" t="inlineStr">
@@ -36071,7 +35556,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P520" t="inlineStr"/>
     </row>
     <row r="521" ht="28" customHeight="1" s="84">
       <c r="A521" t="inlineStr">
@@ -36139,7 +35623,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P521" t="inlineStr"/>
     </row>
     <row r="522" ht="28" customHeight="1" s="84">
       <c r="A522" t="inlineStr">
@@ -36207,7 +35690,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P522" t="inlineStr"/>
     </row>
     <row r="523" ht="28" customHeight="1" s="84">
       <c r="A523" t="inlineStr">
@@ -36275,7 +35757,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P523" t="inlineStr"/>
     </row>
     <row r="524" ht="28" customHeight="1" s="84">
       <c r="A524" t="inlineStr">
@@ -36343,7 +35824,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P524" t="inlineStr"/>
     </row>
     <row r="525" ht="28" customHeight="1" s="84">
       <c r="A525" t="inlineStr">
@@ -36411,7 +35891,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P525" t="inlineStr"/>
     </row>
     <row r="526" ht="28" customHeight="1" s="84">
       <c r="A526" t="inlineStr">
@@ -36479,7 +35958,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P526" t="inlineStr"/>
     </row>
     <row r="527" ht="28" customHeight="1" s="84">
       <c r="A527" t="inlineStr">
@@ -36547,7 +36025,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P527" t="inlineStr"/>
     </row>
     <row r="528" ht="28" customHeight="1" s="84">
       <c r="A528" t="inlineStr">
@@ -36615,7 +36092,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P528" t="inlineStr"/>
     </row>
     <row r="529" ht="28" customHeight="1" s="84">
       <c r="A529" t="inlineStr">
@@ -36683,7 +36159,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P529" t="inlineStr"/>
     </row>
     <row r="530" ht="28" customHeight="1" s="84">
       <c r="A530" t="inlineStr">
@@ -36751,7 +36226,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P530" t="inlineStr"/>
     </row>
     <row r="531" ht="28" customHeight="1" s="84">
       <c r="A531" t="inlineStr">
@@ -36819,7 +36293,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P531" t="inlineStr"/>
     </row>
     <row r="532" ht="28" customHeight="1" s="84">
       <c r="A532" t="inlineStr">
@@ -36887,7 +36360,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P532" t="inlineStr"/>
     </row>
     <row r="533" ht="28" customHeight="1" s="84">
       <c r="A533" t="inlineStr">
@@ -36955,7 +36427,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P533" t="inlineStr"/>
     </row>
     <row r="534" ht="28" customHeight="1" s="84">
       <c r="A534" t="inlineStr">
@@ -37023,7 +36494,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P534" t="inlineStr"/>
     </row>
     <row r="535" ht="28" customHeight="1" s="84">
       <c r="A535" t="inlineStr">
@@ -37091,7 +36561,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P535" t="inlineStr"/>
     </row>
     <row r="536" ht="28" customHeight="1" s="84">
       <c r="A536" t="inlineStr">
@@ -37159,7 +36628,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P536" t="inlineStr"/>
     </row>
     <row r="537" ht="28" customHeight="1" s="84">
       <c r="A537" t="inlineStr">
@@ -37227,7 +36695,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P537" t="inlineStr"/>
     </row>
     <row r="538" ht="28" customHeight="1" s="84">
       <c r="A538" t="inlineStr">
@@ -37295,7 +36762,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P538" t="inlineStr"/>
     </row>
     <row r="539" ht="28" customHeight="1" s="84">
       <c r="A539" t="inlineStr">
@@ -37363,7 +36829,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P539" t="inlineStr"/>
     </row>
     <row r="540" ht="28" customHeight="1" s="84">
       <c r="A540" t="inlineStr">
@@ -37431,7 +36896,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P540" t="inlineStr"/>
     </row>
     <row r="541" ht="28" customHeight="1" s="84">
       <c r="A541" t="inlineStr">
@@ -37499,7 +36963,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P541" t="inlineStr"/>
     </row>
     <row r="542" ht="28" customHeight="1" s="84">
       <c r="A542" t="inlineStr">
@@ -37567,7 +37030,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P542" t="inlineStr"/>
     </row>
     <row r="543" ht="28" customHeight="1" s="84">
       <c r="A543" t="inlineStr">
@@ -37635,7 +37097,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P543" t="inlineStr"/>
     </row>
     <row r="544" ht="28" customHeight="1" s="84">
       <c r="A544" t="inlineStr">
@@ -37703,7 +37164,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P544" t="inlineStr"/>
     </row>
     <row r="545" ht="28" customHeight="1" s="84">
       <c r="A545" t="inlineStr">
@@ -37771,7 +37231,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P545" t="inlineStr"/>
     </row>
     <row r="546" ht="28" customHeight="1" s="84">
       <c r="A546" t="inlineStr">
@@ -37839,7 +37298,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P546" t="inlineStr"/>
     </row>
     <row r="547" ht="28" customHeight="1" s="84">
       <c r="A547" t="inlineStr">
@@ -37907,7 +37365,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P547" t="inlineStr"/>
     </row>
     <row r="548" ht="28" customHeight="1" s="84">
       <c r="A548" t="inlineStr">
@@ -37975,7 +37432,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P548" t="inlineStr"/>
     </row>
     <row r="549" ht="28" customHeight="1" s="84">
       <c r="A549" t="inlineStr">
@@ -38043,7 +37499,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P549" t="inlineStr"/>
     </row>
     <row r="550" ht="28" customHeight="1" s="84">
       <c r="A550" t="inlineStr">
@@ -38111,7 +37566,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P550" t="inlineStr"/>
     </row>
     <row r="551" ht="28" customHeight="1" s="84">
       <c r="A551" t="inlineStr">
@@ -38179,7 +37633,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P551" t="inlineStr"/>
     </row>
     <row r="552" ht="28" customHeight="1" s="84">
       <c r="A552" t="inlineStr">
@@ -38247,7 +37700,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P552" t="inlineStr"/>
     </row>
     <row r="553" ht="28" customHeight="1" s="84">
       <c r="A553" t="inlineStr">
@@ -38315,7 +37767,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P553" t="inlineStr"/>
     </row>
     <row r="554" ht="28" customHeight="1" s="84">
       <c r="A554" t="inlineStr">
@@ -38383,7 +37834,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P554" t="inlineStr"/>
     </row>
     <row r="555" ht="28" customHeight="1" s="84">
       <c r="A555" t="inlineStr">
@@ -38451,7 +37901,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P555" t="inlineStr"/>
     </row>
     <row r="556" ht="28" customHeight="1" s="84">
       <c r="A556" t="inlineStr">
@@ -38519,7 +37968,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P556" t="inlineStr"/>
     </row>
     <row r="557" ht="28" customHeight="1" s="84">
       <c r="A557" t="inlineStr">
@@ -38587,7 +38035,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P557" t="inlineStr"/>
     </row>
     <row r="558" ht="28" customHeight="1" s="84">
       <c r="A558" t="inlineStr">
@@ -38655,7 +38102,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P558" t="inlineStr"/>
     </row>
     <row r="559" ht="28" customHeight="1" s="84">
       <c r="A559" t="inlineStr">
@@ -38723,7 +38169,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P559" t="inlineStr"/>
     </row>
     <row r="560" ht="28" customHeight="1" s="84">
       <c r="A560" t="inlineStr">
@@ -38791,7 +38236,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P560" t="inlineStr"/>
     </row>
     <row r="561" ht="28" customHeight="1" s="84">
       <c r="A561" t="inlineStr">
@@ -38859,7 +38303,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P561" t="inlineStr"/>
     </row>
     <row r="562" ht="28" customHeight="1" s="84">
       <c r="A562" t="inlineStr">
@@ -38927,7 +38370,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P562" t="inlineStr"/>
     </row>
     <row r="563" ht="28" customHeight="1" s="84">
       <c r="A563" t="inlineStr">
@@ -38995,7 +38437,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P563" t="inlineStr"/>
     </row>
     <row r="564" ht="28" customHeight="1" s="84">
       <c r="A564" t="inlineStr">
@@ -39063,7 +38504,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P564" t="inlineStr"/>
     </row>
     <row r="565" ht="28" customHeight="1" s="84">
       <c r="A565" t="inlineStr">
@@ -39131,7 +38571,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P565" t="inlineStr"/>
     </row>
     <row r="566" ht="28" customHeight="1" s="84">
       <c r="A566" t="inlineStr">
@@ -39199,7 +38638,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P566" t="inlineStr"/>
     </row>
     <row r="567" ht="28" customHeight="1" s="84">
       <c r="A567" t="inlineStr">
@@ -39267,7 +38705,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P567" t="inlineStr"/>
     </row>
     <row r="568" ht="28" customHeight="1" s="84">
       <c r="A568" t="inlineStr">
@@ -39335,7 +38772,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P568" t="inlineStr"/>
     </row>
     <row r="569" ht="28" customHeight="1" s="84">
       <c r="A569" t="inlineStr">
@@ -39403,7 +38839,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P569" t="inlineStr"/>
     </row>
     <row r="570" ht="28" customHeight="1" s="84">
       <c r="A570" t="inlineStr">
@@ -39471,7 +38906,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P570" t="inlineStr"/>
     </row>
     <row r="571" ht="28" customHeight="1" s="84">
       <c r="A571" t="inlineStr">
@@ -39539,7 +38973,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P571" t="inlineStr"/>
     </row>
     <row r="572" ht="28" customHeight="1" s="84">
       <c r="A572" t="inlineStr">
@@ -39607,7 +39040,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P572" t="inlineStr"/>
     </row>
     <row r="573" ht="28" customHeight="1" s="84">
       <c r="A573" t="inlineStr">
@@ -39675,7 +39107,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P573" t="inlineStr"/>
     </row>
     <row r="574" ht="28" customHeight="1" s="84">
       <c r="A574" t="inlineStr">
@@ -39743,7 +39174,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P574" t="inlineStr"/>
     </row>
     <row r="575" ht="28" customHeight="1" s="84">
       <c r="A575" t="inlineStr">
@@ -39816,7 +39246,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P575" t="inlineStr"/>
     </row>
     <row r="576" ht="28" customHeight="1" s="84">
       <c r="A576" t="inlineStr">
@@ -39884,7 +39313,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P576" t="inlineStr"/>
     </row>
     <row r="577" ht="28" customHeight="1" s="84">
       <c r="A577" t="inlineStr">
@@ -39957,7 +39385,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P577" t="inlineStr"/>
     </row>
     <row r="578" ht="28" customHeight="1" s="84">
       <c r="A578" t="inlineStr">
@@ -40025,7 +39452,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P578" t="inlineStr"/>
     </row>
     <row r="579" ht="28" customHeight="1" s="84">
       <c r="A579" t="inlineStr">
@@ -40093,7 +39519,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P579" t="inlineStr"/>
     </row>
     <row r="580" ht="28" customHeight="1" s="84">
       <c r="A580" t="inlineStr">
@@ -40161,7 +39586,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P580" t="inlineStr"/>
     </row>
     <row r="581" ht="28" customHeight="1" s="84">
       <c r="A581" t="inlineStr">
@@ -40229,7 +39653,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P581" t="inlineStr"/>
     </row>
     <row r="582" ht="28" customHeight="1" s="84">
       <c r="A582" t="inlineStr">
@@ -40297,7 +39720,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P582" t="inlineStr"/>
     </row>
     <row r="583" ht="28" customHeight="1" s="84">
       <c r="A583" t="inlineStr">
@@ -40365,7 +39787,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P583" t="inlineStr"/>
     </row>
     <row r="584" ht="28" customHeight="1" s="84">
       <c r="A584" t="inlineStr">
@@ -40433,7 +39854,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P584" t="inlineStr"/>
     </row>
     <row r="585" ht="28" customHeight="1" s="84">
       <c r="A585" t="inlineStr">
@@ -40501,7 +39921,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P585" t="inlineStr"/>
     </row>
     <row r="586" ht="28" customHeight="1" s="84">
       <c r="A586" t="inlineStr">
@@ -40569,7 +39988,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P586" t="inlineStr"/>
     </row>
     <row r="587" ht="28" customHeight="1" s="84">
       <c r="A587" t="inlineStr">
@@ -40637,7 +40055,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P587" t="inlineStr"/>
     </row>
     <row r="588" ht="28" customHeight="1" s="84">
       <c r="A588" t="inlineStr">
@@ -40705,7 +40122,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P588" t="inlineStr"/>
     </row>
     <row r="589" ht="28" customHeight="1" s="84">
       <c r="A589" t="inlineStr">
@@ -40773,7 +40189,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P589" t="inlineStr"/>
     </row>
     <row r="590" ht="28" customHeight="1" s="84">
       <c r="A590" t="inlineStr">
@@ -40841,7 +40256,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P590" t="inlineStr"/>
     </row>
     <row r="591" ht="28" customHeight="1" s="84">
       <c r="A591" t="inlineStr">
@@ -40909,7 +40323,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P591" t="inlineStr"/>
     </row>
     <row r="592" ht="28" customHeight="1" s="84">
       <c r="A592" t="inlineStr">
@@ -40977,7 +40390,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P592" t="inlineStr"/>
     </row>
     <row r="593" ht="28" customHeight="1" s="84">
       <c r="A593" t="inlineStr">
@@ -41045,7 +40457,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P593" t="inlineStr"/>
     </row>
     <row r="594" ht="28" customHeight="1" s="84">
       <c r="A594" t="inlineStr">
@@ -41113,7 +40524,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P594" t="inlineStr"/>
     </row>
     <row r="595" ht="28" customHeight="1" s="84">
       <c r="A595" t="inlineStr">
@@ -41181,7 +40591,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P595" t="inlineStr"/>
     </row>
     <row r="596" ht="28" customHeight="1" s="84">
       <c r="A596" t="inlineStr">
@@ -41249,7 +40658,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P596" t="inlineStr"/>
     </row>
     <row r="597" ht="28" customHeight="1" s="84">
       <c r="A597" t="inlineStr">
@@ -41317,7 +40725,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P597" t="inlineStr"/>
     </row>
     <row r="598" ht="28" customHeight="1" s="84">
       <c r="A598" t="inlineStr">
@@ -41385,7 +40792,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P598" t="inlineStr"/>
     </row>
     <row r="599" ht="28" customHeight="1" s="84">
       <c r="A599" t="inlineStr">
@@ -41453,7 +40859,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P599" t="inlineStr"/>
     </row>
     <row r="600" ht="28" customHeight="1" s="84">
       <c r="A600" t="inlineStr">
@@ -41521,7 +40926,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P600" t="inlineStr"/>
     </row>
     <row r="601" ht="28" customHeight="1" s="84">
       <c r="A601" t="inlineStr">
@@ -41589,7 +40993,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P601" t="inlineStr"/>
     </row>
     <row r="602" ht="28" customHeight="1" s="84">
       <c r="A602" t="inlineStr">
@@ -41657,7 +41060,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P602" t="inlineStr"/>
     </row>
     <row r="603" ht="28" customHeight="1" s="84">
       <c r="A603" t="inlineStr">
@@ -41725,7 +41127,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P603" t="inlineStr"/>
     </row>
     <row r="604" ht="28" customHeight="1" s="84">
       <c r="A604" t="inlineStr">
@@ -41793,7 +41194,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P604" t="inlineStr"/>
     </row>
     <row r="605" ht="28" customHeight="1" s="84">
       <c r="A605" t="inlineStr">
@@ -41861,7 +41261,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P605" t="inlineStr"/>
     </row>
     <row r="606" ht="28" customHeight="1" s="84">
       <c r="A606" t="inlineStr">
@@ -41929,7 +41328,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P606" t="inlineStr"/>
     </row>
     <row r="607" ht="28" customHeight="1" s="84">
       <c r="A607" t="inlineStr">
@@ -41997,7 +41395,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P607" t="inlineStr"/>
     </row>
     <row r="608" ht="28" customHeight="1" s="84">
       <c r="A608" t="inlineStr">
@@ -42065,7 +41462,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P608" t="inlineStr"/>
     </row>
     <row r="609" ht="28" customHeight="1" s="84">
       <c r="A609" t="inlineStr">
@@ -42133,7 +41529,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P609" t="inlineStr"/>
     </row>
     <row r="610" ht="28" customHeight="1" s="84">
       <c r="A610" t="inlineStr">
@@ -42201,7 +41596,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P610" t="inlineStr"/>
     </row>
     <row r="611" ht="28" customHeight="1" s="84">
       <c r="A611" t="inlineStr">
@@ -42269,7 +41663,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P611" t="inlineStr"/>
     </row>
     <row r="612" ht="28" customHeight="1" s="84">
       <c r="A612" t="inlineStr">
@@ -42337,7 +41730,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P612" t="inlineStr"/>
     </row>
     <row r="613" ht="28" customHeight="1" s="84">
       <c r="A613" t="inlineStr">
@@ -42405,7 +41797,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P613" t="inlineStr"/>
     </row>
     <row r="614" ht="28" customHeight="1" s="84">
       <c r="A614" t="inlineStr">
@@ -42473,7 +41864,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P614" t="inlineStr"/>
     </row>
     <row r="615" ht="28" customHeight="1" s="84">
       <c r="A615" t="inlineStr">
@@ -42541,7 +41931,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P615" t="inlineStr"/>
     </row>
     <row r="616" ht="28" customHeight="1" s="84">
       <c r="A616" t="inlineStr">
@@ -42609,7 +41998,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P616" t="inlineStr"/>
     </row>
     <row r="617" ht="28" customHeight="1" s="84">
       <c r="A617" t="inlineStr">
@@ -42677,7 +42065,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P617" t="inlineStr"/>
     </row>
     <row r="618" ht="28" customHeight="1" s="84">
       <c r="A618" t="inlineStr">
@@ -42745,7 +42132,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P618" t="inlineStr"/>
     </row>
     <row r="619" ht="28" customHeight="1" s="84">
       <c r="A619" t="inlineStr">
@@ -42813,7 +42199,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P619" t="inlineStr"/>
     </row>
     <row r="620" ht="28" customHeight="1" s="84">
       <c r="A620" t="inlineStr">
@@ -42881,7 +42266,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P620" t="inlineStr"/>
     </row>
     <row r="621" ht="28" customHeight="1" s="84">
       <c r="A621" t="inlineStr">
@@ -42949,7 +42333,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P621" t="inlineStr"/>
     </row>
     <row r="622" ht="28" customHeight="1" s="84">
       <c r="A622" t="inlineStr">
@@ -43017,7 +42400,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P622" t="inlineStr"/>
     </row>
     <row r="623" ht="28" customHeight="1" s="84">
       <c r="A623" t="inlineStr">
@@ -43085,7 +42467,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P623" t="inlineStr"/>
     </row>
     <row r="624" ht="28" customHeight="1" s="84">
       <c r="A624" t="inlineStr">
@@ -43153,7 +42534,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P624" t="inlineStr"/>
     </row>
     <row r="625" ht="28" customHeight="1" s="84">
       <c r="A625" t="inlineStr">
@@ -43221,7 +42601,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P625" t="inlineStr"/>
     </row>
     <row r="626" ht="28" customHeight="1" s="84">
       <c r="A626" t="inlineStr">
@@ -43289,7 +42668,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P626" t="inlineStr"/>
     </row>
     <row r="627" ht="28" customHeight="1" s="84">
       <c r="A627" t="inlineStr">
@@ -43357,7 +42735,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P627" t="inlineStr"/>
     </row>
     <row r="628" ht="28" customHeight="1" s="84">
       <c r="A628" t="inlineStr">
@@ -43425,7 +42802,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P628" t="inlineStr"/>
     </row>
     <row r="629" ht="28" customHeight="1" s="84">
       <c r="A629" t="inlineStr">
@@ -43493,7 +42869,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P629" t="inlineStr"/>
     </row>
     <row r="630" ht="28" customHeight="1" s="84">
       <c r="A630" t="inlineStr">
@@ -43561,7 +42936,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P630" t="inlineStr"/>
     </row>
     <row r="631" ht="28" customHeight="1" s="84">
       <c r="A631" t="inlineStr">
@@ -43629,7 +43003,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P631" t="inlineStr"/>
     </row>
     <row r="632" ht="28" customHeight="1" s="84">
       <c r="A632" t="inlineStr">
@@ -43697,7 +43070,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P632" t="inlineStr"/>
     </row>
     <row r="633" ht="28" customHeight="1" s="84">
       <c r="A633" t="inlineStr">
@@ -43765,7 +43137,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P633" t="inlineStr"/>
     </row>
     <row r="634" ht="28" customHeight="1" s="84">
       <c r="A634" t="inlineStr">
@@ -43833,7 +43204,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P634" t="inlineStr"/>
     </row>
     <row r="635" ht="28" customHeight="1" s="84">
       <c r="A635" t="inlineStr">
@@ -43901,7 +43271,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P635" t="inlineStr"/>
     </row>
     <row r="636" ht="28" customHeight="1" s="84">
       <c r="A636" t="inlineStr">
@@ -43969,7 +43338,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P636" t="inlineStr"/>
     </row>
     <row r="637" ht="28" customHeight="1" s="84">
       <c r="A637" t="inlineStr">
@@ -44037,7 +43405,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P637" t="inlineStr"/>
     </row>
     <row r="638" ht="28" customHeight="1" s="84">
       <c r="A638" t="inlineStr">
@@ -44105,7 +43472,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P638" t="inlineStr"/>
     </row>
     <row r="639" ht="28" customHeight="1" s="84">
       <c r="A639" t="inlineStr">
@@ -44173,7 +43539,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P639" t="inlineStr"/>
     </row>
     <row r="640" ht="28" customHeight="1" s="84">
       <c r="A640" t="inlineStr">
@@ -44241,7 +43606,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P640" t="inlineStr"/>
     </row>
     <row r="641" ht="28" customHeight="1" s="84">
       <c r="A641" t="inlineStr">
@@ -44309,7 +43673,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P641" t="inlineStr"/>
     </row>
     <row r="642" ht="28" customHeight="1" s="84">
       <c r="A642" t="inlineStr">
@@ -44377,7 +43740,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P642" t="inlineStr"/>
     </row>
     <row r="643" ht="28" customHeight="1" s="84">
       <c r="A643" t="inlineStr">
@@ -44445,7 +43807,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P643" t="inlineStr"/>
     </row>
     <row r="644" ht="28" customHeight="1" s="84">
       <c r="A644" t="inlineStr">
@@ -44513,7 +43874,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P644" t="inlineStr"/>
     </row>
     <row r="645" ht="28" customHeight="1" s="84">
       <c r="A645" t="inlineStr">
@@ -44581,7 +43941,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P645" t="inlineStr"/>
     </row>
     <row r="646" ht="28" customHeight="1" s="84">
       <c r="A646" t="inlineStr">
@@ -44649,7 +44008,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P646" t="inlineStr"/>
     </row>
     <row r="647" ht="28" customHeight="1" s="84">
       <c r="A647" t="inlineStr">
@@ -44717,7 +44075,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P647" t="inlineStr"/>
     </row>
     <row r="648" ht="28" customHeight="1" s="84">
       <c r="A648" t="inlineStr">
@@ -44785,7 +44142,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P648" t="inlineStr"/>
     </row>
     <row r="649" ht="28" customHeight="1" s="84">
       <c r="A649" t="inlineStr">
@@ -44853,7 +44209,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P649" t="inlineStr"/>
     </row>
     <row r="650" ht="28" customHeight="1" s="84">
       <c r="A650" t="inlineStr">
@@ -44921,7 +44276,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P650" t="inlineStr"/>
     </row>
     <row r="651" ht="28" customHeight="1" s="84">
       <c r="A651" t="inlineStr">
@@ -44989,7 +44343,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P651" t="inlineStr"/>
     </row>
     <row r="652" ht="28" customHeight="1" s="84">
       <c r="A652" t="inlineStr">
@@ -45057,7 +44410,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P652" t="inlineStr"/>
     </row>
     <row r="653" ht="28" customHeight="1" s="84">
       <c r="A653" t="inlineStr">
@@ -45125,7 +44477,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P653" t="inlineStr"/>
     </row>
     <row r="654" ht="28" customHeight="1" s="84">
       <c r="A654" t="inlineStr">
@@ -45193,7 +44544,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P654" t="inlineStr"/>
     </row>
     <row r="655" ht="28" customHeight="1" s="84">
       <c r="A655" t="inlineStr">
@@ -45261,7 +44611,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P655" t="inlineStr"/>
     </row>
     <row r="656" ht="28" customHeight="1" s="84">
       <c r="A656" t="inlineStr">
@@ -45329,7 +44678,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P656" t="inlineStr"/>
     </row>
     <row r="657" ht="28" customHeight="1" s="84">
       <c r="A657" t="inlineStr">
@@ -45397,7 +44745,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P657" t="inlineStr"/>
     </row>
     <row r="658" ht="28" customHeight="1" s="84">
       <c r="A658" t="inlineStr">
@@ -45465,7 +44812,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P658" t="inlineStr"/>
     </row>
     <row r="659" ht="28" customHeight="1" s="84">
       <c r="A659" t="inlineStr">
@@ -45533,7 +44879,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P659" t="inlineStr"/>
     </row>
     <row r="660" ht="28" customHeight="1" s="84">
       <c r="A660" t="inlineStr">
@@ -45601,7 +44946,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P660" t="inlineStr"/>
     </row>
     <row r="661" ht="28" customHeight="1" s="84">
       <c r="A661" t="inlineStr">
@@ -45669,7 +45013,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P661" t="inlineStr"/>
     </row>
     <row r="662" ht="28" customHeight="1" s="84">
       <c r="A662" t="inlineStr">
@@ -45737,7 +45080,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P662" t="inlineStr"/>
     </row>
     <row r="663" ht="28" customHeight="1" s="84">
       <c r="A663" t="inlineStr">
@@ -45805,7 +45147,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P663" t="inlineStr"/>
     </row>
     <row r="664" ht="28" customHeight="1" s="84">
       <c r="A664" t="inlineStr">
@@ -45873,7 +45214,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P664" t="inlineStr"/>
     </row>
     <row r="665" ht="28" customHeight="1" s="84">
       <c r="A665" t="inlineStr">
@@ -45941,7 +45281,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P665" t="inlineStr"/>
     </row>
     <row r="666" ht="28" customHeight="1" s="84">
       <c r="A666" t="inlineStr">
@@ -46009,7 +45348,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P666" t="inlineStr"/>
     </row>
     <row r="667" ht="28" customHeight="1" s="84">
       <c r="A667" t="inlineStr">
@@ -46077,7 +45415,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P667" t="inlineStr"/>
     </row>
     <row r="668" ht="28" customHeight="1" s="84">
       <c r="A668" t="inlineStr">
@@ -46145,7 +45482,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P668" t="inlineStr"/>
     </row>
     <row r="669" ht="28" customHeight="1" s="84">
       <c r="A669" t="inlineStr">
@@ -46213,7 +45549,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P669" t="inlineStr"/>
     </row>
     <row r="670" ht="28" customHeight="1" s="84">
       <c r="A670" t="inlineStr">
@@ -46281,7 +45616,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P670" t="inlineStr"/>
     </row>
     <row r="671" ht="28" customHeight="1" s="84">
       <c r="A671" t="inlineStr">
@@ -46349,7 +45683,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P671" t="inlineStr"/>
     </row>
     <row r="672" ht="28" customHeight="1" s="84">
       <c r="A672" t="inlineStr">
@@ -46417,7 +45750,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P672" t="inlineStr"/>
     </row>
     <row r="673" ht="28" customHeight="1" s="84">
       <c r="A673" t="inlineStr">
@@ -46485,7 +45817,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P673" t="inlineStr"/>
     </row>
     <row r="674" ht="28" customHeight="1" s="84">
       <c r="A674" t="inlineStr">
@@ -46553,7 +45884,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P674" t="inlineStr"/>
     </row>
     <row r="675" ht="28" customHeight="1" s="84">
       <c r="A675" t="inlineStr">
@@ -46621,7 +45951,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P675" t="inlineStr"/>
     </row>
     <row r="676" ht="28" customHeight="1" s="84">
       <c r="A676" t="inlineStr">
@@ -46689,7 +46018,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P676" t="inlineStr"/>
     </row>
     <row r="677" ht="28" customHeight="1" s="84">
       <c r="A677" t="inlineStr">
@@ -46757,7 +46085,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P677" t="inlineStr"/>
     </row>
     <row r="678" ht="28" customHeight="1" s="84">
       <c r="A678" t="inlineStr">
@@ -46825,7 +46152,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P678" t="inlineStr"/>
     </row>
     <row r="679" ht="28" customHeight="1" s="84">
       <c r="A679" t="inlineStr">
@@ -46893,7 +46219,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P679" t="inlineStr"/>
     </row>
     <row r="680" ht="28" customHeight="1" s="84">
       <c r="A680" t="inlineStr">
@@ -46961,7 +46286,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P680" t="inlineStr"/>
     </row>
     <row r="681" ht="28" customHeight="1" s="84">
       <c r="A681" t="inlineStr">
@@ -47029,7 +46353,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P681" t="inlineStr"/>
     </row>
     <row r="682" ht="28" customHeight="1" s="84">
       <c r="A682" t="inlineStr">
@@ -47097,7 +46420,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P682" t="inlineStr"/>
     </row>
     <row r="683" ht="28" customHeight="1" s="84">
       <c r="A683" t="inlineStr">
@@ -47165,7 +46487,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P683" t="inlineStr"/>
     </row>
     <row r="684" ht="28" customHeight="1" s="84">
       <c r="A684" t="inlineStr">
@@ -47233,7 +46554,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P684" t="inlineStr"/>
     </row>
     <row r="685" ht="28" customHeight="1" s="84">
       <c r="A685" t="inlineStr">
@@ -47301,7 +46621,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P685" t="inlineStr"/>
     </row>
     <row r="686" ht="28" customHeight="1" s="84">
       <c r="A686" t="inlineStr">
@@ -47369,7 +46688,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P686" t="inlineStr"/>
     </row>
     <row r="687" ht="28" customHeight="1" s="84">
       <c r="A687" t="inlineStr">
@@ -47437,7 +46755,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P687" t="inlineStr"/>
     </row>
     <row r="688" ht="28" customHeight="1" s="84">
       <c r="A688" t="inlineStr">
@@ -47505,7 +46822,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P688" t="inlineStr"/>
     </row>
     <row r="689" ht="28" customHeight="1" s="84">
       <c r="A689" t="inlineStr">
@@ -47573,7 +46889,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P689" t="inlineStr"/>
     </row>
     <row r="690" ht="28" customHeight="1" s="84">
       <c r="A690" t="inlineStr">
@@ -47641,7 +46956,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P690" t="inlineStr"/>
     </row>
     <row r="691" ht="28" customHeight="1" s="84">
       <c r="A691" t="inlineStr">
@@ -47709,7 +47023,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P691" t="inlineStr"/>
     </row>
     <row r="692" ht="28" customHeight="1" s="84">
       <c r="A692" t="inlineStr">
@@ -47777,7 +47090,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P692" t="inlineStr"/>
     </row>
     <row r="693" ht="28" customHeight="1" s="84">
       <c r="A693" t="inlineStr">
@@ -47845,7 +47157,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P693" t="inlineStr"/>
     </row>
     <row r="694" ht="28" customHeight="1" s="84">
       <c r="A694" t="inlineStr">
@@ -47913,7 +47224,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P694" t="inlineStr"/>
     </row>
     <row r="695" ht="28" customHeight="1" s="84">
       <c r="A695" t="inlineStr">
@@ -47981,7 +47291,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P695" t="inlineStr"/>
     </row>
     <row r="696" ht="28" customHeight="1" s="84">
       <c r="A696" t="inlineStr">
@@ -48049,7 +47358,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P696" t="inlineStr"/>
     </row>
     <row r="697" ht="28" customHeight="1" s="84">
       <c r="A697" t="inlineStr">
@@ -48117,7 +47425,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P697" t="inlineStr"/>
     </row>
     <row r="698" ht="28" customHeight="1" s="84">
       <c r="A698" t="inlineStr">
@@ -48185,7 +47492,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P698" t="inlineStr"/>
     </row>
     <row r="699" ht="28" customHeight="1" s="84">
       <c r="A699" t="inlineStr">
@@ -48253,7 +47559,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P699" t="inlineStr"/>
     </row>
     <row r="700" ht="28" customHeight="1" s="84">
       <c r="A700" t="inlineStr">
@@ -48321,7 +47626,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P700" t="inlineStr"/>
     </row>
     <row r="701" ht="28" customHeight="1" s="84">
       <c r="A701" t="inlineStr">
@@ -48389,7 +47693,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P701" t="inlineStr"/>
     </row>
     <row r="702" ht="28" customHeight="1" s="84">
       <c r="A702" t="inlineStr">
@@ -48457,7 +47760,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P702" t="inlineStr"/>
     </row>
     <row r="703" ht="28" customHeight="1" s="84">
       <c r="A703" t="inlineStr">
@@ -48525,7 +47827,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P703" t="inlineStr"/>
     </row>
     <row r="704" ht="28" customHeight="1" s="84">
       <c r="A704" t="inlineStr">
@@ -48593,7 +47894,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P704" t="inlineStr"/>
     </row>
     <row r="705" ht="28" customHeight="1" s="84">
       <c r="A705" t="inlineStr">
@@ -48661,7 +47961,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P705" t="inlineStr"/>
     </row>
     <row r="706" ht="28" customHeight="1" s="84">
       <c r="A706" t="inlineStr">
@@ -48729,7 +48028,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P706" t="inlineStr"/>
     </row>
     <row r="707" ht="28" customHeight="1" s="84">
       <c r="A707" t="inlineStr">
@@ -48797,7 +48095,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P707" t="inlineStr"/>
     </row>
     <row r="708" ht="28" customHeight="1" s="84">
       <c r="A708" t="inlineStr">
@@ -48865,7 +48162,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P708" t="inlineStr"/>
     </row>
     <row r="709" ht="28" customHeight="1" s="84">
       <c r="A709" t="inlineStr">
@@ -48933,7 +48229,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P709" t="inlineStr"/>
     </row>
     <row r="710" ht="28" customHeight="1" s="84">
       <c r="A710" t="inlineStr">
@@ -49001,7 +48296,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P710" t="inlineStr"/>
     </row>
     <row r="711" ht="28" customHeight="1" s="84">
       <c r="A711" t="inlineStr">
@@ -49069,7 +48363,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P711" t="inlineStr"/>
     </row>
     <row r="712" ht="28" customHeight="1" s="84">
       <c r="A712" t="inlineStr">
@@ -49137,7 +48430,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P712" t="inlineStr"/>
     </row>
     <row r="713" ht="28" customHeight="1" s="84">
       <c r="A713" t="inlineStr">
@@ -49205,7 +48497,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P713" t="inlineStr"/>
     </row>
     <row r="714" ht="28" customHeight="1" s="84">
       <c r="A714" t="inlineStr">
@@ -49273,7 +48564,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P714" t="inlineStr"/>
     </row>
     <row r="715" ht="28" customHeight="1" s="84">
       <c r="A715" t="inlineStr">
@@ -49341,7 +48631,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P715" t="inlineStr"/>
     </row>
     <row r="716" ht="28" customHeight="1" s="84">
       <c r="A716" t="inlineStr">
@@ -49409,7 +48698,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P716" t="inlineStr"/>
     </row>
     <row r="717" ht="28" customHeight="1" s="84">
       <c r="A717" t="inlineStr">
@@ -49477,7 +48765,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P717" t="inlineStr"/>
     </row>
     <row r="718" ht="28" customHeight="1" s="84">
       <c r="A718" t="inlineStr">
@@ -49545,7 +48832,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P718" t="inlineStr"/>
     </row>
     <row r="719" ht="28" customHeight="1" s="84">
       <c r="A719" t="inlineStr">
@@ -49613,7 +48899,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P719" t="inlineStr"/>
     </row>
     <row r="720" ht="28" customHeight="1" s="84">
       <c r="A720" t="inlineStr">
@@ -49681,7 +48966,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P720" t="inlineStr"/>
     </row>
     <row r="721" ht="28" customHeight="1" s="84">
       <c r="A721" t="inlineStr">
@@ -49749,7 +49033,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P721" t="inlineStr"/>
     </row>
     <row r="722" ht="28" customHeight="1" s="84">
       <c r="A722" t="inlineStr">
@@ -49817,7 +49100,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P722" t="inlineStr"/>
     </row>
     <row r="723" ht="28" customHeight="1" s="84">
       <c r="A723" t="inlineStr">
@@ -49885,7 +49167,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P723" t="inlineStr"/>
     </row>
     <row r="724" ht="28" customHeight="1" s="84">
       <c r="A724" t="inlineStr">
@@ -49953,7 +49234,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P724" t="inlineStr"/>
     </row>
     <row r="725" ht="28" customHeight="1" s="84">
       <c r="A725" t="inlineStr">
@@ -50021,7 +49301,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P725" t="inlineStr"/>
     </row>
     <row r="726" ht="28" customHeight="1" s="84">
       <c r="A726" t="inlineStr">
@@ -50089,7 +49368,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P726" t="inlineStr"/>
     </row>
     <row r="727" ht="28" customHeight="1" s="84">
       <c r="A727" t="inlineStr">
@@ -50157,7 +49435,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P727" t="inlineStr"/>
     </row>
     <row r="728" ht="28" customHeight="1" s="84">
       <c r="A728" t="inlineStr">
@@ -50225,7 +49502,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P728" t="inlineStr"/>
     </row>
     <row r="729" ht="28" customHeight="1" s="84">
       <c r="A729" t="inlineStr">
@@ -50293,7 +49569,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P729" t="inlineStr"/>
     </row>
     <row r="730" ht="28" customHeight="1" s="84">
       <c r="A730" t="inlineStr">
@@ -50361,7 +49636,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P730" t="inlineStr"/>
     </row>
     <row r="731" ht="28" customHeight="1" s="84">
       <c r="A731" t="inlineStr">
@@ -50429,7 +49703,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P731" t="inlineStr"/>
     </row>
     <row r="732" ht="28" customHeight="1" s="84">
       <c r="A732" t="inlineStr">
@@ -50497,7 +49770,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P732" t="inlineStr"/>
     </row>
     <row r="733" ht="28" customHeight="1" s="84">
       <c r="A733" t="inlineStr">
@@ -50565,7 +49837,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P733" t="inlineStr"/>
     </row>
     <row r="734" ht="28" customHeight="1" s="84">
       <c r="A734" t="inlineStr">
@@ -50633,7 +49904,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P734" t="inlineStr"/>
     </row>
     <row r="735" ht="28" customHeight="1" s="84">
       <c r="A735" t="inlineStr">
@@ -50701,7 +49971,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P735" t="inlineStr"/>
     </row>
     <row r="736" ht="28" customHeight="1" s="84">
       <c r="A736" t="inlineStr">
@@ -50769,7 +50038,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P736" t="inlineStr"/>
     </row>
     <row r="737" ht="28" customHeight="1" s="84">
       <c r="A737" t="inlineStr">
@@ -50842,7 +50110,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P737" t="inlineStr"/>
     </row>
     <row r="738" ht="28" customHeight="1" s="84">
       <c r="A738" t="inlineStr">
@@ -50915,7 +50182,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P738" t="inlineStr"/>
     </row>
     <row r="739" ht="28" customHeight="1" s="84">
       <c r="A739" t="inlineStr">
@@ -50988,7 +50254,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P739" t="inlineStr"/>
     </row>
     <row r="740" ht="28" customHeight="1" s="84">
       <c r="A740" t="inlineStr">
@@ -51061,7 +50326,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P740" t="inlineStr"/>
     </row>
     <row r="741" ht="28" customHeight="1" s="84">
       <c r="A741" t="inlineStr">
@@ -51134,7 +50398,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P741" t="inlineStr"/>
     </row>
     <row r="742" ht="28" customHeight="1" s="84">
       <c r="A742" t="inlineStr">
@@ -51207,7 +50470,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P742" t="inlineStr"/>
     </row>
     <row r="743" ht="28" customHeight="1" s="84">
       <c r="A743" t="inlineStr">
@@ -51280,7 +50542,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P743" t="inlineStr"/>
     </row>
     <row r="744" ht="28" customHeight="1" s="84">
       <c r="A744" t="inlineStr">
@@ -51353,7 +50614,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P744" t="inlineStr"/>
     </row>
     <row r="745" ht="28" customHeight="1" s="84">
       <c r="A745" t="inlineStr">
@@ -51426,7 +50686,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P745" t="inlineStr"/>
     </row>
     <row r="746" ht="28" customHeight="1" s="84">
       <c r="A746" t="inlineStr">
@@ -51499,7 +50758,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P746" t="inlineStr"/>
     </row>
     <row r="747" ht="28" customHeight="1" s="84">
       <c r="A747" t="inlineStr">
@@ -51572,7 +50830,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P747" t="inlineStr"/>
     </row>
     <row r="748" ht="28" customHeight="1" s="84">
       <c r="A748" t="inlineStr">
@@ -51645,7 +50902,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P748" t="inlineStr"/>
     </row>
     <row r="749" ht="28" customHeight="1" s="84">
       <c r="A749" t="inlineStr">
@@ -51718,7 +50974,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P749" t="inlineStr"/>
     </row>
     <row r="750" ht="28" customHeight="1" s="84">
       <c r="A750" t="inlineStr">
@@ -51791,7 +51046,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P750" t="inlineStr"/>
     </row>
     <row r="751" ht="28" customHeight="1" s="84">
       <c r="A751" t="inlineStr">
@@ -51864,7 +51118,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P751" t="inlineStr"/>
     </row>
     <row r="752" ht="28" customHeight="1" s="84">
       <c r="A752" t="inlineStr">
@@ -51937,7 +51190,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P752" t="inlineStr"/>
     </row>
     <row r="753" ht="28" customHeight="1" s="84">
       <c r="A753" t="inlineStr">
@@ -52010,7 +51262,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P753" t="inlineStr"/>
     </row>
     <row r="754" ht="28" customHeight="1" s="84">
       <c r="A754" t="inlineStr">
@@ -52083,7 +51334,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P754" t="inlineStr"/>
     </row>
     <row r="755" ht="28" customHeight="1" s="84">
       <c r="A755" t="inlineStr">
@@ -52156,7 +51406,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P755" t="inlineStr"/>
     </row>
     <row r="756" ht="28" customHeight="1" s="84">
       <c r="A756" t="inlineStr">
@@ -52229,7 +51478,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P756" t="inlineStr"/>
     </row>
     <row r="757" ht="28" customHeight="1" s="84">
       <c r="A757" t="inlineStr">
@@ -52302,7 +51550,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P757" t="inlineStr"/>
     </row>
     <row r="758" ht="28" customHeight="1" s="84">
       <c r="A758" t="inlineStr">
@@ -52375,7 +51622,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P758" t="inlineStr"/>
     </row>
     <row r="759" ht="28" customHeight="1" s="84">
       <c r="A759" t="inlineStr">
@@ -52448,7 +51694,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P759" t="inlineStr"/>
     </row>
     <row r="760" ht="28" customHeight="1" s="84">
       <c r="A760" t="inlineStr">
@@ -52521,7 +51766,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P760" t="inlineStr"/>
     </row>
     <row r="761" ht="28" customHeight="1" s="84">
       <c r="A761" t="inlineStr">
@@ -52594,7 +51838,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P761" t="inlineStr"/>
     </row>
     <row r="762" ht="28" customHeight="1" s="84">
       <c r="A762" t="inlineStr">
@@ -52667,7 +51910,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P762" t="inlineStr"/>
     </row>
     <row r="763" ht="28" customHeight="1" s="84">
       <c r="A763" t="inlineStr">
@@ -52740,7 +51982,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P763" t="inlineStr"/>
     </row>
     <row r="764" ht="28" customHeight="1" s="84">
       <c r="A764" t="inlineStr">
@@ -52813,7 +52054,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P764" t="inlineStr"/>
     </row>
     <row r="765" ht="28" customHeight="1" s="84">
       <c r="A765" t="inlineStr">
@@ -52886,7 +52126,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P765" t="inlineStr"/>
     </row>
     <row r="766" ht="28" customHeight="1" s="84">
       <c r="A766" t="inlineStr">
@@ -52959,7 +52198,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P766" t="inlineStr"/>
     </row>
     <row r="767" ht="28" customHeight="1" s="84">
       <c r="A767" t="inlineStr">
@@ -53032,7 +52270,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P767" t="inlineStr"/>
     </row>
     <row r="768" ht="28" customHeight="1" s="84">
       <c r="A768" t="inlineStr">
@@ -53105,7 +52342,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P768" t="inlineStr"/>
     </row>
     <row r="769" ht="28" customHeight="1" s="84">
       <c r="A769" t="inlineStr">
@@ -53178,7 +52414,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P769" t="inlineStr"/>
     </row>
     <row r="770" ht="28" customHeight="1" s="84">
       <c r="A770" t="inlineStr">
@@ -53246,7 +52481,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P770" t="inlineStr"/>
     </row>
     <row r="771" ht="28" customHeight="1" s="84">
       <c r="A771" t="inlineStr">
@@ -53314,7 +52548,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P771" t="inlineStr"/>
     </row>
     <row r="772" ht="28" customHeight="1" s="84">
       <c r="A772" t="inlineStr">
@@ -53382,7 +52615,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P772" t="inlineStr"/>
     </row>
     <row r="773" ht="28" customHeight="1" s="84">
       <c r="A773" t="inlineStr">
@@ -53450,7 +52682,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P773" t="inlineStr"/>
     </row>
     <row r="774" ht="28" customHeight="1" s="84">
       <c r="A774" t="inlineStr">
@@ -53518,7 +52749,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P774" t="inlineStr"/>
     </row>
     <row r="775" ht="28" customHeight="1" s="84">
       <c r="A775" t="inlineStr">
@@ -53586,7 +52816,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P775" t="inlineStr"/>
     </row>
     <row r="776" ht="28" customHeight="1" s="84">
       <c r="A776" t="inlineStr">
@@ -53654,7 +52883,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P776" t="inlineStr"/>
     </row>
     <row r="777" ht="28" customHeight="1" s="84">
       <c r="A777" t="inlineStr">
@@ -53722,7 +52950,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P777" t="inlineStr"/>
     </row>
     <row r="778" ht="28" customHeight="1" s="84">
       <c r="A778" t="inlineStr">
@@ -53790,7 +53017,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P778" t="inlineStr"/>
     </row>
     <row r="779" ht="28" customHeight="1" s="84">
       <c r="A779" t="inlineStr">
@@ -53858,7 +53084,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P779" t="inlineStr"/>
     </row>
     <row r="780" ht="28" customHeight="1" s="84">
       <c r="A780" t="inlineStr">
@@ -53926,7 +53151,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P780" t="inlineStr"/>
     </row>
     <row r="781" ht="28" customHeight="1" s="84">
       <c r="A781" t="inlineStr">
@@ -53994,7 +53218,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P781" t="inlineStr"/>
     </row>
     <row r="782" ht="28" customHeight="1" s="84">
       <c r="A782" t="inlineStr">
@@ -54062,7 +53285,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P782" t="inlineStr"/>
     </row>
     <row r="783" ht="28" customHeight="1" s="84">
       <c r="A783" t="inlineStr">
@@ -54130,7 +53352,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P783" t="inlineStr"/>
     </row>
     <row r="784" ht="28" customHeight="1" s="84">
       <c r="A784" t="inlineStr">
@@ -54198,7 +53419,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P784" t="inlineStr"/>
     </row>
     <row r="785" ht="28" customHeight="1" s="84">
       <c r="A785" t="inlineStr">
@@ -54266,7 +53486,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P785" t="inlineStr"/>
     </row>
     <row r="786" ht="28" customHeight="1" s="84">
       <c r="A786" t="inlineStr">
@@ -54334,7 +53553,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P786" t="inlineStr"/>
     </row>
     <row r="787" ht="28" customHeight="1" s="84">
       <c r="A787" t="inlineStr">
@@ -54402,7 +53620,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P787" t="inlineStr"/>
     </row>
     <row r="788" ht="28" customHeight="1" s="84">
       <c r="A788" t="inlineStr">
@@ -54470,7 +53687,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P788" t="inlineStr"/>
     </row>
     <row r="789" ht="28" customHeight="1" s="84">
       <c r="A789" t="inlineStr">
@@ -54538,7 +53754,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P789" t="inlineStr"/>
     </row>
     <row r="790" ht="28" customHeight="1" s="84">
       <c r="A790" t="inlineStr">
@@ -54606,7 +53821,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P790" t="inlineStr"/>
     </row>
     <row r="791" ht="28" customHeight="1" s="84">
       <c r="A791" t="inlineStr">
@@ -54674,7 +53888,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P791" t="inlineStr"/>
     </row>
     <row r="792" ht="28" customHeight="1" s="84">
       <c r="A792" t="inlineStr">
@@ -54742,7 +53955,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P792" t="inlineStr"/>
     </row>
     <row r="793" ht="28" customHeight="1" s="84">
       <c r="A793" t="inlineStr">
@@ -54810,7 +54022,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P793" t="inlineStr"/>
     </row>
     <row r="794" ht="28" customHeight="1" s="84">
       <c r="A794" t="inlineStr">
@@ -54878,7 +54089,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P794" t="inlineStr"/>
     </row>
     <row r="795" ht="28" customHeight="1" s="84">
       <c r="A795" t="inlineStr">
@@ -54946,7 +54156,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P795" t="inlineStr"/>
     </row>
     <row r="796" ht="28" customHeight="1" s="84">
       <c r="A796" t="inlineStr">
@@ -55014,7 +54223,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P796" t="inlineStr"/>
     </row>
     <row r="797" ht="28" customHeight="1" s="84">
       <c r="A797" t="inlineStr">
@@ -55082,7 +54290,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P797" t="inlineStr"/>
     </row>
     <row r="798" ht="28" customHeight="1" s="84">
       <c r="A798" t="inlineStr">
@@ -55150,7 +54357,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P798" t="inlineStr"/>
     </row>
     <row r="799" ht="28" customHeight="1" s="84">
       <c r="A799" t="inlineStr">
@@ -55218,7 +54424,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P799" t="inlineStr"/>
     </row>
     <row r="800" ht="28" customHeight="1" s="84">
       <c r="A800" t="inlineStr">
@@ -55286,7 +54491,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P800" t="inlineStr"/>
     </row>
     <row r="801" ht="28" customHeight="1" s="84">
       <c r="A801" t="inlineStr">
@@ -55354,7 +54558,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P801" t="inlineStr"/>
     </row>
     <row r="802" ht="28" customHeight="1" s="84">
       <c r="A802" t="inlineStr">
@@ -55422,7 +54625,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P802" t="inlineStr"/>
     </row>
     <row r="803" ht="28" customHeight="1" s="84">
       <c r="A803" t="inlineStr">
@@ -55490,7 +54692,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P803" t="inlineStr"/>
     </row>
     <row r="804" ht="28" customHeight="1" s="84">
       <c r="A804" t="inlineStr">
@@ -55558,7 +54759,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P804" t="inlineStr"/>
     </row>
     <row r="805" ht="28" customHeight="1" s="84">
       <c r="A805" t="inlineStr">
@@ -55626,7 +54826,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P805" t="inlineStr"/>
     </row>
     <row r="806" ht="28" customHeight="1" s="84">
       <c r="A806" t="inlineStr">
@@ -55694,7 +54893,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P806" t="inlineStr"/>
     </row>
     <row r="807" ht="28" customHeight="1" s="84">
       <c r="A807" t="inlineStr">
@@ -55762,7 +54960,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P807" t="inlineStr"/>
     </row>
     <row r="808" ht="28" customHeight="1" s="84">
       <c r="A808" t="inlineStr">
@@ -55830,7 +55027,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P808" t="inlineStr"/>
     </row>
     <row r="809" ht="28" customHeight="1" s="84">
       <c r="A809" t="inlineStr">
@@ -55898,7 +55094,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P809" t="inlineStr"/>
     </row>
     <row r="810" ht="28" customHeight="1" s="84">
       <c r="A810" t="inlineStr">
@@ -55966,7 +55161,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P810" t="inlineStr"/>
     </row>
     <row r="811" ht="28" customHeight="1" s="84">
       <c r="A811" t="inlineStr">
@@ -56039,7 +55233,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P811" t="inlineStr"/>
     </row>
     <row r="812" ht="28" customHeight="1" s="84">
       <c r="A812" t="inlineStr">
@@ -56112,7 +55305,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P812" t="inlineStr"/>
     </row>
     <row r="813" ht="28" customHeight="1" s="84">
       <c r="A813" t="inlineStr">
@@ -56185,7 +55377,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P813" t="inlineStr"/>
     </row>
     <row r="814" ht="28" customHeight="1" s="84">
       <c r="A814" t="inlineStr">
@@ -56258,7 +55449,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P814" t="inlineStr"/>
     </row>
     <row r="815" ht="28" customHeight="1" s="84">
       <c r="A815" t="inlineStr">
@@ -56331,7 +55521,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P815" t="inlineStr"/>
     </row>
     <row r="816" ht="28" customHeight="1" s="84">
       <c r="A816" t="inlineStr">
@@ -56404,7 +55593,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P816" t="inlineStr"/>
     </row>
     <row r="817" ht="28" customHeight="1" s="84">
       <c r="A817" t="inlineStr">
@@ -56477,7 +55665,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P817" t="inlineStr"/>
     </row>
     <row r="818" ht="28" customHeight="1" s="84">
       <c r="A818" t="inlineStr">
@@ -56550,7 +55737,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P818" t="inlineStr"/>
     </row>
     <row r="819" ht="28" customHeight="1" s="84">
       <c r="A819" t="inlineStr">
@@ -56623,7 +55809,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P819" t="inlineStr"/>
     </row>
     <row r="820" ht="28" customHeight="1" s="84">
       <c r="A820" t="inlineStr">
@@ -56696,7 +55881,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P820" t="inlineStr"/>
     </row>
     <row r="821" ht="28" customHeight="1" s="84">
       <c r="A821" t="inlineStr">
@@ -56769,7 +55953,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P821" t="inlineStr"/>
     </row>
     <row r="822" ht="28" customHeight="1" s="84">
       <c r="A822" t="inlineStr">
@@ -56842,7 +56025,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P822" t="inlineStr"/>
     </row>
     <row r="823" ht="28" customHeight="1" s="84">
       <c r="A823" t="inlineStr">
@@ -56915,7 +56097,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P823" t="inlineStr"/>
     </row>
     <row r="824" ht="28" customHeight="1" s="84">
       <c r="A824" t="inlineStr">
@@ -56988,7 +56169,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P824" t="inlineStr"/>
     </row>
     <row r="825" ht="28" customHeight="1" s="84">
       <c r="A825" t="inlineStr">
@@ -57061,7 +56241,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P825" t="inlineStr"/>
     </row>
     <row r="826" ht="28" customHeight="1" s="84">
       <c r="A826" t="inlineStr">
@@ -57134,7 +56313,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P826" t="inlineStr"/>
     </row>
     <row r="827" ht="28" customHeight="1" s="84">
       <c r="A827" t="inlineStr">
@@ -57207,7 +56385,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P827" t="inlineStr"/>
     </row>
     <row r="828" ht="28" customHeight="1" s="84">
       <c r="A828" t="inlineStr">
@@ -57280,7 +56457,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P828" t="inlineStr"/>
     </row>
     <row r="829" ht="28" customHeight="1" s="84">
       <c r="A829" t="inlineStr">
@@ -57353,7 +56529,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P829" t="inlineStr"/>
     </row>
     <row r="830" ht="28" customHeight="1" s="84">
       <c r="A830" t="inlineStr">
@@ -57426,7 +56601,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P830" t="inlineStr"/>
     </row>
     <row r="831" ht="28" customHeight="1" s="84">
       <c r="A831" t="inlineStr">
@@ -57499,7 +56673,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P831" t="inlineStr"/>
     </row>
     <row r="832" ht="28" customHeight="1" s="84">
       <c r="A832" t="inlineStr">
@@ -57572,7 +56745,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P832" t="inlineStr"/>
     </row>
     <row r="833" ht="28" customHeight="1" s="84">
       <c r="A833" t="inlineStr">
@@ -57645,7 +56817,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P833" t="inlineStr"/>
     </row>
     <row r="834" ht="28" customHeight="1" s="84">
       <c r="A834" t="inlineStr">
@@ -57718,7 +56889,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P834" t="inlineStr"/>
     </row>
     <row r="835" ht="28" customHeight="1" s="84">
       <c r="A835" t="inlineStr">
@@ -57786,15 +56956,484 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P835" t="inlineStr"/>
-    </row>
-    <row r="836" ht="28" customHeight="1" s="84"/>
-    <row r="837" ht="28" customHeight="1" s="84"/>
-    <row r="838" ht="28" customHeight="1" s="84"/>
-    <row r="839" ht="28" customHeight="1" s="84"/>
-    <row r="840" ht="28" customHeight="1" s="84"/>
-    <row r="841" ht="28" customHeight="1" s="84"/>
-    <row r="842" ht="28" customHeight="1" s="84"/>
+    </row>
+    <row r="836" ht="28" customHeight="1" s="84">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>INS-ARG-0103</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Universidad Juan Agustín Maza</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>Universidad Juan Agustín Maza</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>Villa Nueva</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L836" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+        </is>
+      </c>
+      <c r="M836" t="inlineStr">
+        <is>
+          <t>city_ar_geonames_3832661</t>
+        </is>
+      </c>
+      <c r="N836" t="inlineStr">
+        <is>
+          <t>AR-M</t>
+        </is>
+      </c>
+      <c r="O836" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="837" ht="28" customHeight="1" s="84">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>INS-BRA-0086</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Oeste do Pará</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Oeste do Pará</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>Santarem</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L837" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M837" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3389353</t>
+        </is>
+      </c>
+      <c r="N837" t="inlineStr">
+        <is>
+          <t>BR-PA</t>
+        </is>
+      </c>
+      <c r="O837" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="838" ht="28" customHeight="1" s="84">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>INS-BRA-0183</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>Universidade Federal do ABC</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>Santo Andre</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L838" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M838" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3449701</t>
+        </is>
+      </c>
+      <c r="N838" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="O838" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="839" ht="28" customHeight="1" s="84">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>INS-VEN-0014</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Experimental de Guayana</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Experimental de Guayana</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>Puerto Ordaz</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>https://www.uneg.edu.ve/</t>
+        </is>
+      </c>
+      <c r="L839" t="inlineStr">
+        <is>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
+      <c r="M839" t="inlineStr">
+        <is>
+          <t>city_ve_geonames_3629655</t>
+        </is>
+      </c>
+      <c r="N839" t="inlineStr">
+        <is>
+          <t>VE-F</t>
+        </is>
+      </c>
+      <c r="O839" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="840" ht="28" customHeight="1" s="84">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>INS-BRA-0037</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Goiás</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Goiás</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>Anapolis</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L840" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M840" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3472287</t>
+        </is>
+      </c>
+      <c r="N840" t="inlineStr">
+        <is>
+          <t>BR-GO</t>
+        </is>
+      </c>
+      <c r="O840" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P840" t="inlineStr"/>
+    </row>
+    <row r="841" ht="28" customHeight="1" s="84">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>INS-BRA-0111</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Instituto Federal do Sertão Pernambucano</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>Instituto Federal do Sertão Pernambucano</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>Petrolina</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>Federal Institute</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3392242</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>BR-PE</t>
+        </is>
+      </c>
+      <c r="O841" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P841" t="inlineStr"/>
+    </row>
+    <row r="842" ht="28" customHeight="1" s="84">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>INS-BRA-0114</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Vale do São Francisco</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Vale do São Francisco</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>Petrolina</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3392242</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>BR-PE</t>
+        </is>
+      </c>
+      <c r="O842" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P842" t="inlineStr"/>
+    </row>
     <row r="843" ht="28" customHeight="1" s="84"/>
     <row r="844" ht="28" customHeight="1" s="84"/>
     <row r="845" ht="28" customHeight="1" s="84"/>
@@ -58872,7 +58511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P49"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59008,8 +58647,6 @@
           <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59017,7 +58654,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
@@ -59072,8 +58709,6 @@
           <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59081,7 +58716,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
@@ -59136,8 +58771,6 @@
           <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59145,7 +58778,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
@@ -59200,8 +58833,6 @@
           <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59209,39 +58840,39 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INS-ARG-0103</t>
+          <t>INS-BOL-0008</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Universidad Juan Agustín Maza</t>
+          <t>Universidad Nacional Siglo XX</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Universidad Juan Agustín Maza</t>
+          <t>Universidad Nacional Siglo XX</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Guaymallén</t>
+          <t>Llallagua</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -59251,7 +58882,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -59261,11 +58892,9 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59273,24 +58902,24 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INS-BOL-0008</t>
+          <t>INS-BOL-0011</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Universidad Nacional Siglo XX</t>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Universidad Nacional Siglo XX</t>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -59305,7 +58934,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Llallagua</t>
+          <t>Warisata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -59328,8 +58957,6 @@
           <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59337,24 +58964,24 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INS-BOL-0011</t>
+          <t>INS-BOL-0013</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -59369,7 +58996,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warisata</t>
+          <t>Kuruyuki</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -59392,8 +59019,6 @@
           <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59401,39 +59026,39 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INS-BOL-0013</t>
+          <t>INS-BRA-0054</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+          <t>Universidade Federal da Grande Dourados</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+          <t>Universidade Federal da Grande Dourados</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kuruyuki</t>
+          <t>Dourados</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -59453,11 +59078,9 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59465,24 +59088,24 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INS-BRA-0037</t>
+          <t>INS-BRA-0056</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Universidade Estadual de Goiás</t>
+          <t>Universidade Estadual de Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Universidade Estadual de Goiás</t>
+          <t>Universidade Estadual de Mato Grosso do Sul</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -59497,7 +59120,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Dourados</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -59520,8 +59143,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59529,24 +59150,24 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INS-BRA-0054</t>
+          <t>INS-BRA-0065</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Universidade Federal da Grande Dourados</t>
+          <t>Universidade Federal de Viçosa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Universidade Federal da Grande Dourados</t>
+          <t>Universidade Federal de Viçosa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -59561,7 +59182,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dourados</t>
+          <t>Viçosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -59584,8 +59205,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59593,24 +59212,24 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INS-BRA-0056</t>
+          <t>INS-BRA-0067</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Universidade Estadual de Mato Grosso do Sul</t>
+          <t>Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Universidade Estadual de Mato Grosso do Sul</t>
+          <t>Universidade Federal de Lavras</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -59625,7 +59244,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dourados</t>
+          <t>Lavras</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -59648,8 +59267,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59657,24 +59274,24 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INS-BRA-0065</t>
+          <t>INS-BRA-0073</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Universidade Federal de Viçosa</t>
+          <t>Universidade Federal de Itajubá</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Universidade Federal de Viçosa</t>
+          <t>Universidade Federal de Itajubá</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -59689,12 +59306,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Viçosa</t>
+          <t>Itajubá</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Technical University</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -59712,8 +59329,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59721,24 +59336,24 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INS-BRA-0067</t>
+          <t>INS-BRA-0079</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Universidade Federal de Lavras</t>
+          <t>Universidade de Itaúna</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Universidade Federal de Lavras</t>
+          <t>Universidade de Itaúna</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -59753,7 +59368,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lavras</t>
+          <t>Itaúna</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -59763,7 +59378,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -59776,8 +59391,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59785,24 +59398,24 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INS-BRA-0073</t>
+          <t>INS-BRA-0133</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Universidade Federal de Itajubá</t>
+          <t>Universidade do Grande Rio</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Universidade Federal de Itajubá</t>
+          <t>Universidade do Grande Rio</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -59817,17 +59430,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Itajubá</t>
+          <t>Duque de Caxias</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Technical University</t>
+          <t>University</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -59840,8 +59453,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59849,24 +59460,24 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>INS-BRA-0079</t>
+          <t>INS-BRA-0144</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Universidade de Itaúna</t>
+          <t>Instituto Federal Farroupilha</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Universidade de Itaúna</t>
+          <t>Instituto Federal Farroupilha</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -59881,17 +59492,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Itaúna</t>
+          <t>Santa Maria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Federal Institute</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -59904,8 +59515,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59913,24 +59522,24 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>INS-BRA-0086</t>
+          <t>INS-BRA-0148</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Universidade Federal do Oeste do Pará</t>
+          <t>Universidade Federal do Rio Grande</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Universidade Federal do Oeste do Pará</t>
+          <t>Universidade Federal do Rio Grande</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -59945,7 +59554,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Santarém</t>
+          <t>Rio Grande</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -59968,8 +59577,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -59977,24 +59584,24 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>INS-BRA-0111</t>
+          <t>INS-BRA-0150</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Instituto Federal do Sertão Pernambucano</t>
+          <t>Universidade Federal de Santa Maria</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Instituto Federal do Sertão Pernambucano</t>
+          <t>Universidade Federal de Santa Maria</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -60009,12 +59616,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Petrolina</t>
+          <t>Santa Maria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Federal Institute</t>
+          <t>University</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -60032,8 +59639,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60041,24 +59646,24 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>INS-BRA-0114</t>
+          <t>INS-BRA-0157</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Universidade Federal do Vale do São Francisco</t>
+          <t>Universidade Franciscana</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Universidade Federal do Vale do São Francisco</t>
+          <t>Universidade Franciscana</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -60073,7 +59678,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Petrolina</t>
+          <t>Santa Maria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -60083,7 +59688,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -60096,8 +59701,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60105,24 +59708,24 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>INS-BRA-0133</t>
+          <t>INS-BRA-0160</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Universidade do Grande Rio</t>
+          <t>Universidade Regional Integrada do Alto Uruguai e das Missões</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Universidade do Grande Rio</t>
+          <t>Universidade Regional Integrada do Alto Uruguai e das Missões</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -60137,7 +59740,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Erechim</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -60160,8 +59763,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60169,24 +59770,24 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>INS-BRA-0144</t>
+          <t>INS-BRA-0161</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Instituto Federal Farroupilha</t>
+          <t>Universidade de Caxias do Sul</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Instituto Federal Farroupilha</t>
+          <t>Universidade de Caxias do Sul</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -60201,17 +59802,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Santa Maria</t>
+          <t>Caxias do Sul</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Federal Institute</t>
+          <t>University</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -60224,8 +59825,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60233,24 +59832,24 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>INS-BRA-0148</t>
+          <t>INS-BRA-0162</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Universidade Federal do Rio Grande</t>
+          <t>Universidade de Cruz Alta</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Universidade Federal do Rio Grande</t>
+          <t>Universidade de Cruz Alta</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -60265,7 +59864,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rio Grande</t>
+          <t>Cruz Alta</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -60275,7 +59874,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -60288,8 +59887,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60297,24 +59894,24 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>INS-BRA-0150</t>
+          <t>INS-BRA-0164</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Universidade Federal de Santa Maria</t>
+          <t>Universidade do Vale do Taquari</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Universidade Federal de Santa Maria</t>
+          <t>Universidade do Vale do Taquari</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -60329,7 +59926,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Santa Maria</t>
+          <t>Lajeado</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -60339,7 +59936,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -60352,8 +59949,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60361,24 +59956,24 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INS-BRA-0157</t>
+          <t>INS-BRA-0172</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Universidade Franciscana</t>
+          <t>Universidade Federal da Fronteira Sul</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Universidade Franciscana</t>
+          <t>Universidade Federal da Fronteira Sul</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -60393,7 +59988,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Santa Maria</t>
+          <t>Chapecó</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -60403,7 +59998,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -60416,8 +60011,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60425,24 +60018,24 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INS-BRA-0160</t>
+          <t>INS-BRA-0178</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Universidade Regional Integrada do Alto Uruguai e das Missões</t>
+          <t>Universidade do Oeste de Santa Catarina</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Universidade Regional Integrada do Alto Uruguai e das Missões</t>
+          <t>Universidade do Oeste de Santa Catarina</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -60457,7 +60050,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Erechim</t>
+          <t>Joaçaba</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -60480,8 +60073,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60489,24 +60080,24 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INS-BRA-0161</t>
+          <t>INS-BRA-0179</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Universidade de Caxias do Sul</t>
+          <t>Universidade do Planalto Catarinense</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Universidade de Caxias do Sul</t>
+          <t>Universidade do Planalto Catarinense</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -60521,7 +60112,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Caxias do Sul</t>
+          <t>Lages</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -60544,8 +60135,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60553,24 +60142,24 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INS-BRA-0162</t>
+          <t>INS-BRA-0184</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Universidade de Cruz Alta</t>
+          <t>Universidade Federal de São Carlos</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Universidade de Cruz Alta</t>
+          <t>Universidade Federal de São Carlos</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -60585,7 +60174,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cruz Alta</t>
+          <t>São Carlos</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -60595,7 +60184,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -60608,8 +60197,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60617,24 +60204,24 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INS-BRA-0164</t>
+          <t>INS-BRA-0189</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Universidade do Vale do Taquari</t>
+          <t>Universidade Estadual de Campinas</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Universidade do Vale do Taquari</t>
+          <t>Universidade Estadual de Campinas</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -60649,7 +60236,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lajeado</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -60659,7 +60246,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -60672,8 +60259,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60681,24 +60266,24 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>INS-BRA-0172</t>
+          <t>INS-BRA-0205</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Universidade Federal da Fronteira Sul</t>
+          <t>Pontifícia Universidade Católica de Campinas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Universidade Federal da Fronteira Sul</t>
+          <t>Pontifícia Universidade Católica de Campinas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -60713,7 +60298,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chapecó</t>
+          <t>Campinas</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -60723,7 +60308,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -60736,8 +60321,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60745,24 +60328,24 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>INS-BRA-0178</t>
+          <t>INS-BRA-0214</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Universidade do Oeste de Santa Catarina</t>
+          <t>Universidade São Francisco</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Universidade do Oeste de Santa Catarina</t>
+          <t>Universidade São Francisco</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -60777,7 +60360,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Joaçaba</t>
+          <t>Bragança Paulista</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -60800,8 +60383,6 @@
           <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60809,39 +60390,39 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>INS-BRA-0179</t>
+          <t>INS-COL-0021</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Universidade do Planalto Catarinense</t>
+          <t>Universidad de Pamplona</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Universidade do Planalto Catarinense</t>
+          <t>Universidad de Pamplona</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lages</t>
+          <t>Pamplona</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -60851,7 +60432,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -60861,11 +60442,9 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>https://snies.mineducacion.gov.co/portal/Informes-e-indicadores/Perfiles-de-las-Instituciones-de-Educacion-Superior/</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60873,49 +60452,49 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INS-BRA-0183</t>
+          <t>INS-GUY-0002</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Universidade Federal do ABC</t>
+          <t>Texila American University</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Universidade Federal do ABC</t>
+          <t>Texila American University</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Santo André</t>
+          <t>Providence</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Medical University</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -60923,13 +60502,16 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>https://tau.edu.gy/</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>https://nac.gov.gy/ | https://education.gov.gy/</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -60937,39 +60519,39 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>INS-BRA-0184</t>
+          <t>INS-PRY-0038</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Universidade Federal de São Carlos</t>
+          <t>Universidad Nacional de Canindeyú</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Universidade Federal de São Carlos</t>
+          <t>Universidad Nacional de Canindeyú</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>São Carlos</t>
+          <t>Saltos del Guairá</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -60989,11 +60571,9 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>https://cones.gov.py/universidades/</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61001,39 +60581,39 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>INS-BRA-0189</t>
+          <t>INS-PRY-0056</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Universidade Estadual de Campinas</t>
+          <t>Universidad Santa Clara de Asís</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Universidade Estadual de Campinas</t>
+          <t>Universidad Santa Clara de Asís</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Caaguazú</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -61043,7 +60623,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -61053,11 +60633,9 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>https://cones.gov.py/universidades/</t>
+        </is>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61065,49 +60643,49 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>INS-BRA-0205</t>
+          <t>INS-PER-0028</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pontifícia Universidade Católica de Campinas</t>
+          <t>Universidad Nacional Agraria de la Selva</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pontifícia Universidade Católica de Campinas</t>
+          <t>Universidad Nacional Agraria de la Selva</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Campinas</t>
+          <t>Tingo María</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Agricultural University</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -61117,11 +60695,9 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61129,49 +60705,49 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>INS-BRA-0214</t>
+          <t>INS-PER-0032</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Universidade São Francisco</t>
+          <t>Universidad Nacional Intercultural de Quillabamba</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Universidade São Francisco</t>
+          <t>Universidad Nacional Intercultural de Quillabamba</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bragança Paulista</t>
+          <t>Quillabamba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Intercultural University</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -61181,11 +60757,9 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
       <c r="O36" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61193,44 +60767,44 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>INS-COL-0021</t>
+          <t>INS-PER-0073</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Universidad de Pamplona</t>
+          <t>Universidad Nacional Intercultural de la Selva Central Juan Santos Atahualpa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Universidad de Pamplona</t>
+          <t>Universidad Nacional Intercultural de la Selva Central Juan Santos Atahualpa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pamplona</t>
+          <t>Chanchamayo</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Intercultural University</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -61245,11 +60819,9 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://snies.mineducacion.gov.co/portal/Informes-e-indicadores/Perfiles-de-las-Instituciones-de-Educacion-Superior/</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61257,49 +60829,49 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>INS-GUY-0002</t>
+          <t>INS-PER-0093</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Texila American University</t>
+          <t>Universidad Nacional Autónoma de Huanta</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Texila American University</t>
+          <t>Universidad Nacional Autónoma de Huanta</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Providence</t>
+          <t>Huanta</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Medical University</t>
+          <t>University</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -61307,18 +60879,11 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>https://tau.edu.gy/</t>
-        </is>
-      </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://nac.gov.gy/ | https://education.gov.gy/</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
       <c r="O38" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61326,39 +60891,39 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_GEOGRAPHY_AMBIGUOUS</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>INS-PRY-0038</t>
+          <t>INS-VEN-0020</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Canindeyú</t>
+          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Canindeyú</t>
+          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Saltos del Guairá</t>
+          <t>Santa Bárbara del Zulia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -61376,13 +60941,16 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>https://www.unesur.edu.ve/</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://cones.gov.py/universidades/</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61390,49 +60958,49 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>INS-PRY-0056</t>
+          <t>INS-VEN-0032</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Universidad Santa Clara de Asís</t>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Universidad Santa Clara de Asís</t>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Caaguazú</t>
+          <t>Mantecal</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Technical University</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -61442,11 +61010,9 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://cones.gov.py/universidades/</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
       <c r="O40" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61454,39 +61020,34 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>INS-PER-0028</t>
+          <t>INS-VEN-0043</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Universidad Nacional Agraria de la Selva</t>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Universidad Nacional Agraria de la Selva</t>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Tingo María</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -61506,11 +61067,9 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61518,49 +61077,49 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>INS-PER-0032</t>
+          <t>INS-VEN-0077</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Universidad Nacional Intercultural de Quillabamba</t>
+          <t>Universidad Bicentenaria de Aragua</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Universidad Nacional Intercultural de Quillabamba</t>
+          <t>Universidad Bicentenaria de Aragua</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Quillabamba</t>
+          <t>San Joaquín de Turmero</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Intercultural University</t>
+          <t>University</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -61568,13 +61127,16 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>https://uba.edu.ve/</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>REVIEW_REQUIRED</t>
@@ -61582,465 +61144,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>INS-PER-0073</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Intercultural de la Selva Central Juan Santos Atahualpa</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Intercultural de la Selva Central Juan Santos Atahualpa</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Chanchamayo</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Intercultural University</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>INS-PER-0093</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Autónoma de Huanta</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Autónoma de Huanta</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Huanta</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>INS-VEN-0014</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Experimental de Guayana</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Experimental de Guayana</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Puerto Ordaz</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>https://www.uneg.edu.ve/</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>INS-VEN-0020</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Santa Bárbara del Zulia</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>https://www.unesur.edu.ve/</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>INS-VEN-0032</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Mantecal</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Technical University</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>INS-VEN-0043</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>INS-VEN-0077</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Universidad Bicentenaria de Aragua</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Universidad Bicentenaria de Aragua</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>San Joaquín de Turmero</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>https://uba.edu.ve/</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>CITY_OR_REGION_EVIDENCE_AMBIGUOUS_OR_MISSING</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>

--- a/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
@@ -902,7 +902,6 @@
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="84">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -57296,7 +57295,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P840" t="inlineStr"/>
     </row>
     <row r="841" ht="28" customHeight="1" s="84">
       <c r="A841" t="inlineStr">
@@ -57364,7 +57362,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P841" t="inlineStr"/>
     </row>
     <row r="842" ht="28" customHeight="1" s="84">
       <c r="A842" t="inlineStr">
@@ -57432,7 +57429,6 @@
           <t>SOURCE_MATCHED</t>
         </is>
       </c>
-      <c r="P842" t="inlineStr"/>
     </row>
     <row r="843" ht="28" customHeight="1" s="84"/>
     <row r="844" ht="28" customHeight="1" s="84"/>
@@ -58511,7 +58507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58596,2558 +58592,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>INS-ARG-0005</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Universidad Nacional de Avellaneda</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Universidad Nacional de Avellaneda</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Avellaneda</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INS-ARG-0012</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Universidad Nacional de los Comechingones</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Universidad Nacional de los Comechingones</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Villa de Merlo</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INS-ARG-0068</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Universidad Provincial de Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Universidad Provincial de Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INS-ARG-0072</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Universidad Adventista del Plata</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Universidad Adventista del Plata</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ARG</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Libertador San Martín</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>INS-BOL-0008</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Siglo XX</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Siglo XX</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Llallagua</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>INS-BOL-0011</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Warisata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INS-BOL-0013</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Kuruyuki</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>INS-BRA-0054</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Universidade Federal da Grande Dourados</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Universidade Federal da Grande Dourados</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Dourados</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>INS-BRA-0056</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Universidade Estadual de Mato Grosso do Sul</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Universidade Estadual de Mato Grosso do Sul</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Dourados</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INS-BRA-0065</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Universidade Federal de Viçosa</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Universidade Federal de Viçosa</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Viçosa</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>INS-BRA-0067</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Universidade Federal de Lavras</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Universidade Federal de Lavras</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Lavras</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>INS-BRA-0073</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Universidade Federal de Itajubá</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Universidade Federal de Itajubá</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Itajubá</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Technical University</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>INS-BRA-0079</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Universidade de Itaúna</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Universidade de Itaúna</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Itaúna</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>INS-BRA-0133</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Universidade do Grande Rio</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Universidade do Grande Rio</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Duque de Caxias</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>INS-BRA-0144</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Instituto Federal Farroupilha</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Instituto Federal Farroupilha</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Santa Maria</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Federal Institute</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>INS-BRA-0148</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Universidade Federal do Rio Grande</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Universidade Federal do Rio Grande</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Rio Grande</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>INS-BRA-0150</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Universidade Federal de Santa Maria</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Universidade Federal de Santa Maria</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Santa Maria</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>INS-BRA-0157</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Universidade Franciscana</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Universidade Franciscana</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Santa Maria</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>INS-BRA-0160</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Universidade Regional Integrada do Alto Uruguai e das Missões</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Universidade Regional Integrada do Alto Uruguai e das Missões</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Erechim</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>INS-BRA-0161</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Universidade de Caxias do Sul</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Universidade de Caxias do Sul</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Caxias do Sul</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>INS-BRA-0162</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Universidade de Cruz Alta</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Universidade de Cruz Alta</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Cruz Alta</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>INS-BRA-0164</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Universidade do Vale do Taquari</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Universidade do Vale do Taquari</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Lajeado</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>INS-BRA-0172</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Universidade Federal da Fronteira Sul</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Universidade Federal da Fronteira Sul</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Chapecó</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>INS-BRA-0178</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Universidade do Oeste de Santa Catarina</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Universidade do Oeste de Santa Catarina</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Joaçaba</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>INS-BRA-0179</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Universidade do Planalto Catarinense</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Universidade do Planalto Catarinense</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Lages</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>INS-BRA-0184</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Universidade Federal de São Carlos</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Universidade Federal de São Carlos</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>São Carlos</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>INS-BRA-0189</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Universidade Estadual de Campinas</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Universidade Estadual de Campinas</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Campinas</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>INS-BRA-0205</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Pontifícia Universidade Católica de Campinas</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Pontifícia Universidade Católica de Campinas</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Campinas</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>INS-BRA-0214</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Universidade São Francisco</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Universidade São Francisco</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Bragança Paulista</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>INS-COL-0021</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Universidad de Pamplona</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Universidad de Pamplona</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Colombia</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>COL</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Pamplona</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://snies.mineducacion.gov.co/portal/Informes-e-indicadores/Perfiles-de-las-Instituciones-de-Educacion-Superior/</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>INS-GUY-0002</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Texila American University</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Texila American University</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Guyana</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>GUY</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Providence</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Medical University</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>https://tau.edu.gy/</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>https://nac.gov.gy/ | https://education.gov.gy/</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>INS-PRY-0038</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Universidad Nacional de Canindeyú</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Universidad Nacional de Canindeyú</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>PRY</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Saltos del Guairá</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>https://cones.gov.py/universidades/</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>INS-PRY-0056</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Universidad Santa Clara de Asís</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Universidad Santa Clara de Asís</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>PRY</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Caaguazú</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>https://cones.gov.py/universidades/</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>INS-PER-0028</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Agraria de la Selva</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Agraria de la Selva</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Tingo María</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>INS-PER-0032</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Intercultural de Quillabamba</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Intercultural de Quillabamba</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Quillabamba</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Intercultural University</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>INS-PER-0073</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Intercultural de la Selva Central Juan Santos Atahualpa</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Intercultural de la Selva Central Juan Santos Atahualpa</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Chanchamayo</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Intercultural University</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>INS-PER-0093</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Autónoma de Huanta</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Autónoma de Huanta</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Huanta</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_GEOGRAPHY_AMBIGUOUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>INS-VEN-0020</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Santa Bárbara del Zulia</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>https://www.unesur.edu.ve/</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>INS-VEN-0032</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Mantecal</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Technical University</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>INS-VEN-0043</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>INS-VEN-0077</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Universidad Bicentenaria de Aragua</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Universidad Bicentenaria de Aragua</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>San Joaquín de Turmero</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>https://uba.edu.ve/</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P842"/>
+  <dimension ref="A1:P868"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="84" min="1" max="1"/>
@@ -902,6 +902,7 @@
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="84">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -57430,32 +57431,1848 @@
         </is>
       </c>
     </row>
-    <row r="843" ht="28" customHeight="1" s="84"/>
-    <row r="844" ht="28" customHeight="1" s="84"/>
-    <row r="845" ht="28" customHeight="1" s="84"/>
-    <row r="846" ht="28" customHeight="1" s="84"/>
-    <row r="847" ht="28" customHeight="1" s="84"/>
-    <row r="848" ht="28" customHeight="1" s="84"/>
-    <row r="849" ht="28" customHeight="1" s="84"/>
-    <row r="850" ht="28" customHeight="1" s="84"/>
-    <row r="851" ht="28" customHeight="1" s="84"/>
-    <row r="852" ht="28" customHeight="1" s="84"/>
-    <row r="853" ht="28" customHeight="1" s="84"/>
-    <row r="854" ht="28" customHeight="1" s="84"/>
-    <row r="855" ht="28" customHeight="1" s="84"/>
-    <row r="856" ht="28" customHeight="1" s="84"/>
-    <row r="857" ht="28" customHeight="1" s="84"/>
-    <row r="858" ht="28" customHeight="1" s="84"/>
-    <row r="859" ht="28" customHeight="1" s="84"/>
-    <row r="860" ht="28" customHeight="1" s="84"/>
-    <row r="861" ht="28" customHeight="1" s="84"/>
-    <row r="862" ht="28" customHeight="1" s="84"/>
-    <row r="863" ht="28" customHeight="1" s="84"/>
-    <row r="864" ht="28" customHeight="1" s="84"/>
-    <row r="865" ht="28" customHeight="1" s="84"/>
-    <row r="866" ht="28" customHeight="1" s="84"/>
-    <row r="867" ht="28" customHeight="1" s="84"/>
-    <row r="868" ht="28" customHeight="1" s="84"/>
+    <row r="843" ht="28" customHeight="1" s="84">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>INS-ARG-0005</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Avellaneda</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Avellaneda</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>Avellaneda</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>city_ar_geonames_3436230</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>AR-S</t>
+        </is>
+      </c>
+      <c r="O843" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P843" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="844" ht="28" customHeight="1" s="84">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>INS-BRA-0054</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Universidade Federal da Grande Dourados</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>Universidade Federal da Grande Dourados</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>Dourados</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3464460</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>BR-MS</t>
+        </is>
+      </c>
+      <c r="O844" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P844" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="845" ht="28" customHeight="1" s="84">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>INS-BRA-0056</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Mato Grosso do Sul</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Mato Grosso do Sul</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>Dourados</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3464460</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>BR-MS</t>
+        </is>
+      </c>
+      <c r="O845" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P845" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="846" ht="28" customHeight="1" s="84">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>INS-BRA-0065</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Viçosa</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Viçosa</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>Viçosa</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3445133</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="O846" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P846" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="847" ht="28" customHeight="1" s="84">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>INS-BRA-0067</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Lavras</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Lavras</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>Lavras</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3458696</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="O847" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P847" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="848" ht="28" customHeight="1" s="84">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>INS-BRA-0073</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Itajubá</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Itajubá</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>Itajubá</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>Technical University</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3460834</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="O848" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P848" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="849" ht="28" customHeight="1" s="84">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>INS-BRA-0079</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Universidade de Itaúna</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>Universidade de Itaúna</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>Itaúna</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3460584</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>BR-MG</t>
+        </is>
+      </c>
+      <c r="O849" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P849" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="850" ht="28" customHeight="1" s="84">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>INS-BRA-0144</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Instituto Federal Farroupilha</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>Instituto Federal Farroupilha</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>Santa Maria</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>Federal Institute</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3450083</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="O850" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="851" ht="28" customHeight="1" s="84">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>INS-BRA-0148</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio Grande</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>Universidade Federal do Rio Grande</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>Rio Grande</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3451138</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="O851" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="852" ht="28" customHeight="1" s="84">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>INS-BRA-0150</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Santa Maria</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Santa Maria</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>Santa Maria</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3450083</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="O852" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P852" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="853" ht="28" customHeight="1" s="84">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>INS-BRA-0157</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Universidade Franciscana</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>Universidade Franciscana</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>Santa Maria</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3450083</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="O853" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P853" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="854" ht="28" customHeight="1" s="84">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>INS-BRA-0160</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Universidade Regional Integrada do Alto Uruguai e das Missões</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>Universidade Regional Integrada do Alto Uruguai e das Missões</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>Erechim</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3464073</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="O854" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P854" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="855" ht="28" customHeight="1" s="84">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>INS-BRA-0161</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Universidade de Caxias do Sul</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>Universidade de Caxias do Sul</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>Caxias do Sul</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3466537</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="O855" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P855" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="856" ht="28" customHeight="1" s="84">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>INS-BRA-0162</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Universidade de Cruz Alta</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>Universidade de Cruz Alta</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>Cruz Alta</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3465108</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="O856" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P856" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="857" ht="28" customHeight="1" s="84">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>INS-BRA-0164</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Universidade do Vale do Taquari</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>Universidade do Vale do Taquari</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>Lajeado</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3459035</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>BR-RS</t>
+        </is>
+      </c>
+      <c r="O857" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P857" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="858" ht="28" customHeight="1" s="84">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>INS-BRA-0172</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Universidade Federal da Fronteira Sul</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>Universidade Federal da Fronteira Sul</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>Chapecó</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3466296</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>BR-SC</t>
+        </is>
+      </c>
+      <c r="O858" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P858" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="859" ht="28" customHeight="1" s="84">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>INS-BRA-0178</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Universidade do Oeste de Santa Catarina</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>Universidade do Oeste de Santa Catarina</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>Joaçaba</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3459869</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>BR-SC</t>
+        </is>
+      </c>
+      <c r="O859" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="860" ht="28" customHeight="1" s="84">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>INS-BRA-0179</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Universidade do Planalto Catarinense</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>Universidade do Planalto Catarinense</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>Lages</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3458930</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>BR-SC</t>
+        </is>
+      </c>
+      <c r="O860" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P860" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="861" ht="28" customHeight="1" s="84">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>INS-BRA-0184</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Universidade Federal de São Carlos</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>Universidade Federal de São Carlos</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>São Carlos</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3449319</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="O861" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P861" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="862" ht="28" customHeight="1" s="84">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>INS-BRA-0189</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Campinas</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Campinas</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>Campinas</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3467865</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="O862" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="863" ht="28" customHeight="1" s="84">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>INS-BRA-0205</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Pontifícia Universidade Católica de Campinas</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>Pontifícia Universidade Católica de Campinas</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>Campinas</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3467865</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="O863" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="864" ht="28" customHeight="1" s="84">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>INS-BRA-0214</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Universidade São Francisco</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>Universidade São Francisco</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>Bragança Paulista</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>city_br_geonames_3469092</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>BR-SP</t>
+        </is>
+      </c>
+      <c r="O864" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P864" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="865" ht="28" customHeight="1" s="84">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>INS-COL-0021</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Universidad de Pamplona</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>Universidad de Pamplona</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>COL</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>Pamplona</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>https://snies.mineducacion.gov.co/portal/Informes-e-indicadores/Perfiles-de-las-Instituciones-de-Educacion-Superior/</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>city_co_geonames_3673045</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>CO-NSA</t>
+        </is>
+      </c>
+      <c r="O865" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P865" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="866" ht="28" customHeight="1" s="84">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>INS-GUY-0002</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Texila American University</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>Texila American University</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>GUY</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>Providence</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>Medical University</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>https://tau.edu.gy/</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>https://nac.gov.gy/ | https://education.gov.gy/</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>city_gy_official_providence</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>GY-DE</t>
+        </is>
+      </c>
+      <c r="O866" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="867" ht="28" customHeight="1" s="84">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>INS-PER-0073</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Intercultural de la Selva Central Juan Santos Atahualpa</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Intercultural de la Selva Central Juan Santos Atahualpa</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>Chanchamayo</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>Intercultural University</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>city_pe_official_chanchamayo</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>PE-JUN</t>
+        </is>
+      </c>
+      <c r="O867" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="868" ht="28" customHeight="1" s="84">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>INS-VEN-0077</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Universidad Bicentenaria de Aragua</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>Universidad Bicentenaria de Aragua</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>Turmero</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>https://uba.edu.ve/</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>city_ve_turmero</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>VE-D</t>
+        </is>
+      </c>
+      <c r="O868" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
     <row r="869" ht="28" customHeight="1" s="84"/>
     <row r="870" ht="28" customHeight="1" s="84"/>
     <row r="871" ht="28" customHeight="1" s="84"/>
@@ -58507,7 +60324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58592,6 +60409,936 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INS-ARG-0012</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de los Comechingones</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de los Comechingones</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Villa de Merlo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>INS-ARG-0068</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Universidad Provincial de Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Universidad Provincial de Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>INS-ARG-0072</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Universidad Adventista del Plata</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Universidad Adventista del Plata</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Libertador San Martín</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>INS-BOL-0008</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Siglo XX</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Siglo XX</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Llallagua</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>INS-BOL-0011</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Warisata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>INS-BOL-0013</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Kuruyuki</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>INS-BRA-0133</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Universidade do Grande Rio</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Universidade do Grande Rio</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Duque de Caxias</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>INS-PRY-0038</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Canindeyú</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Canindeyú</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Saltos del Guairá</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://cones.gov.py/universidades/</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>INS-PRY-0056</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Universidad Santa Clara de Asís</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Universidad Santa Clara de Asís</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Caaguazú</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://cones.gov.py/universidades/</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>INS-PER-0028</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Agraria de la Selva</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Agraria de la Selva</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tingo María</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Agricultural University</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>INS-PER-0032</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Intercultural de Quillabamba</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Intercultural de Quillabamba</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Quillabamba</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Intercultural University</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>INS-PER-0093</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Autónoma de Huanta</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Autónoma de Huanta</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Huanta</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_GEOGRAPHY_AMBIGUOUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>INS-VEN-0020</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Santa Bárbara del Zulia</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://www.unesur.edu.ve/</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>INS-VEN-0032</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Mantecal</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Technical University</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>INS-VEN-0043</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Agricultural University</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>REVIEW_REQUIRED</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P868"/>
+  <dimension ref="A1:P869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="84" min="1" max="1"/>
@@ -36352,7 +36352,7 @@
       </c>
       <c r="N532" t="inlineStr">
         <is>
-          <t>EC-G</t>
+          <t>EC-SE</t>
         </is>
       </c>
       <c r="O532" t="inlineStr">
@@ -59273,7 +59273,78 @@
         </is>
       </c>
     </row>
-    <row r="869" ht="28" customHeight="1" s="84"/>
+    <row r="869" ht="28" customHeight="1" s="84">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>INS-PER-0028</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Agraria de la Selva</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Agraria de la Selva</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>Tingo María</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>Agricultural University</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>city_pe_geonames_3691348</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>PE-HUC</t>
+        </is>
+      </c>
+      <c r="O869" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P869" t="inlineStr">
+        <is>
+          <t>REGISTRY_CITY_CORROBORATED_MAIN_CAMPUS_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
     <row r="870" ht="28" customHeight="1" s="84"/>
     <row r="871" ht="28" customHeight="1" s="84"/>
     <row r="872" ht="28" customHeight="1" s="84"/>
@@ -60324,7 +60395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60970,17 +61041,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INS-PER-0028</t>
+          <t>INS-PER-0032</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Universidad Nacional Agraria de la Selva</t>
+          <t>Universidad Nacional Intercultural de Quillabamba</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Universidad Nacional Agraria de la Selva</t>
+          <t>Universidad Nacional Intercultural de Quillabamba</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -60995,12 +61066,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tingo María</t>
+          <t>Quillabamba</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Agricultural University</t>
+          <t>Intercultural University</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -61032,17 +61103,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INS-PER-0032</t>
+          <t>INS-PER-0093</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Universidad Nacional Intercultural de Quillabamba</t>
+          <t>Universidad Nacional Autónoma de Huanta</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Universidad Nacional Intercultural de Quillabamba</t>
+          <t>Universidad Nacional Autónoma de Huanta</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -61057,12 +61128,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Quillabamba</t>
+          <t>Huanta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Intercultural University</t>
+          <t>University</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -61087,39 +61158,39 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+          <t>OFFICIAL_ADDRESS_GEOGRAPHY_AMBIGUOUS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INS-PER-0093</t>
+          <t>INS-VEN-0020</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Universidad Nacional Autónoma de Huanta</t>
+          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Universidad Nacional Autónoma de Huanta</t>
+          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Huanta</t>
+          <t>Santa Bárbara del Zulia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -61137,9 +61208,14 @@
           <t>Active</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://www.unesur.edu.ve/</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -61149,24 +61225,24 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>OFFICIAL_ADDRESS_GEOGRAPHY_AMBIGUOUS</t>
+          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>INS-VEN-0020</t>
+          <t>INS-VEN-0032</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -61181,12 +61257,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Santa Bárbara del Zulia</t>
+          <t>Mantecal</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Technical University</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -61197,11 +61273,6 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>Active</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>https://www.unesur.edu.ve/</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -61223,17 +61294,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>INS-VEN-0032</t>
+          <t>INS-VEN-0043</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -61246,14 +61317,9 @@
           <t>VEN</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Mantecal</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Technical University</t>
+          <t>Agricultural University</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -61277,63 +61343,6 @@
         </is>
       </c>
       <c r="P15" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>INS-VEN-0043</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
         <is>
           <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>

--- a/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P869"/>
+  <dimension ref="A1:P873"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="84" min="1" max="1"/>
@@ -59345,10 +59345,299 @@
         </is>
       </c>
     </row>
-    <row r="870" ht="28" customHeight="1" s="84"/>
-    <row r="871" ht="28" customHeight="1" s="84"/>
-    <row r="872" ht="28" customHeight="1" s="84"/>
-    <row r="873" ht="28" customHeight="1" s="84"/>
+    <row r="870" ht="28" customHeight="1" s="84">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>INS-ARG-0072</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Universidad Adventista del Plata</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>Universidad Adventista del Plata</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>Libertador San Martin</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>city_ar_official_libertador_san_martin</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>AR-E</t>
+        </is>
+      </c>
+      <c r="O870" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P870" t="inlineStr">
+        <is>
+          <t>PRIMARY_ADDRESS_SEARCH_INDEX_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="871" ht="28" customHeight="1" s="84">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>INS-PER-0032</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Intercultural de Quillabamba</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Intercultural de Quillabamba</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>Quillabamba</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>Intercultural University</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>city_pe_official_quillabamba</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>PE-CUS</t>
+        </is>
+      </c>
+      <c r="O871" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P871" t="inlineStr">
+        <is>
+          <t>PRIMARY_ADDRESS_SEARCH_INDEX_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="872" ht="28" customHeight="1" s="84">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>INS-PER-0093</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Autónoma de Huanta</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Autónoma de Huanta</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Peru</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>PER</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>Luricocha</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>city_pe_official_luricocha</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>PE-AYA</t>
+        </is>
+      </c>
+      <c r="O872" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P872" t="inlineStr">
+        <is>
+          <t>PRIMARY_ADDRESS_SEARCH_INDEX_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="873" ht="28" customHeight="1" s="84">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>INS-VEN-0020</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>Santa Barbara del Zulia</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>https://www.unesur.edu.ve/</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>city_ve_official_santa_barbara_del_zulia</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>VE-V</t>
+        </is>
+      </c>
+      <c r="O873" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P873" t="inlineStr">
+        <is>
+          <t>PRIMARY_ADDRESS_SEARCH_INDEX_NOT_LIVE_VERIFIED</t>
+        </is>
+      </c>
+    </row>
     <row r="874" ht="28" customHeight="1" s="84"/>
     <row r="875" ht="28" customHeight="1" s="84"/>
     <row r="876" ht="28" customHeight="1" s="84"/>
@@ -60395,7 +60684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60607,32 +60896,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INS-ARG-0072</t>
+          <t>INS-BOL-0008</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Universidad Adventista del Plata</t>
+          <t>Universidad Nacional Siglo XX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Universidad Adventista del Plata</t>
+          <t>Universidad Nacional Siglo XX</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Libertador San Martín</t>
+          <t>Llallagua</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -60642,7 +60931,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -60652,7 +60941,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -60669,17 +60958,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INS-BOL-0008</t>
+          <t>INS-BOL-0011</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Universidad Nacional Siglo XX</t>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Universidad Nacional Siglo XX</t>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -60694,7 +60983,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Llallagua</t>
+          <t>Warisata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -60731,17 +61020,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INS-BOL-0011</t>
+          <t>INS-BOL-0013</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -60756,7 +61045,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Warisata</t>
+          <t>Kuruyuki</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -60793,32 +61082,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INS-BOL-0013</t>
+          <t>INS-BRA-0133</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+          <t>Universidade do Grande Rio</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+          <t>Universidade do Grande Rio</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Kuruyuki</t>
+          <t>Duque de Caxias</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -60828,7 +61117,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -60838,7 +61127,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -60855,32 +61144,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INS-BRA-0133</t>
+          <t>INS-PRY-0038</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Universidade do Grande Rio</t>
+          <t>Universidad Nacional de Canindeyú</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Universidade do Grande Rio</t>
+          <t>Universidad Nacional de Canindeyú</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Saltos del Guairá</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -60890,7 +61179,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -60900,7 +61189,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+          <t>https://cones.gov.py/universidades/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -60917,17 +61206,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INS-PRY-0038</t>
+          <t>INS-PRY-0056</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Canindeyú</t>
+          <t>Universidad Santa Clara de Asís</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Canindeyú</t>
+          <t>Universidad Santa Clara de Asís</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -60942,7 +61231,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saltos del Guairá</t>
+          <t>Caaguazú</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -60952,7 +61241,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -60979,42 +61268,42 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>INS-PRY-0056</t>
+          <t>INS-VEN-0032</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Universidad Santa Clara de Asís</t>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Universidad Santa Clara de Asís</t>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Caaguazú</t>
+          <t>Mantecal</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Technical University</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -61024,7 +61313,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://cones.gov.py/universidades/</t>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -61041,37 +61330,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>INS-PER-0032</t>
+          <t>INS-VEN-0043</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Universidad Nacional Intercultural de Quillabamba</t>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Universidad Nacional Intercultural de Quillabamba</t>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Quillabamba</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Intercultural University</t>
+          <t>Agricultural University</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -61086,7 +61370,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -61095,254 +61379,6 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>INS-PER-0093</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Autónoma de Huanta</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Autónoma de Huanta</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Peru</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>PER</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Huanta</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://www.sunedu.gob.pe/lista-de-universidades-licenciadas/</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_GEOGRAPHY_AMBIGUOUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>INS-VEN-0020</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Experimental Sur del Lago Jesús María Semprum</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Santa Bárbara del Zulia</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>https://www.unesur.edu.ve/</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>INS-VEN-0032</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Mantecal</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Technical University</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>INS-VEN-0043</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
         <is>
           <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>

--- a/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P873"/>
+  <dimension ref="A1:P875"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="84" min="1" max="1"/>
@@ -59638,8 +59638,140 @@
         </is>
       </c>
     </row>
-    <row r="874" ht="28" customHeight="1" s="84"/>
-    <row r="875" ht="28" customHeight="1" s="84"/>
+    <row r="874" ht="28" customHeight="1" s="84">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>INS-ARG-0068</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Universidad Provincial de Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>Universidad Provincial de Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>ARG</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>city_ar_official_laguna_blanca</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>AR-P</t>
+        </is>
+      </c>
+      <c r="O874" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
+    <row r="875" ht="28" customHeight="1" s="84">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>INS-PRY-0038</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Canindeyú</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Canindeyú</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>Salto del Guaira</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>https://cones.gov.py/universidades/</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>city_py_salto_del_guaira</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>PY-14</t>
+        </is>
+      </c>
+      <c r="O875" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+    </row>
     <row r="876" ht="28" customHeight="1" s="84"/>
     <row r="877" ht="28" customHeight="1" s="84"/>
     <row r="878" ht="28" customHeight="1" s="84"/>
@@ -60684,7 +60816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60834,32 +60966,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>INS-ARG-0068</t>
+          <t>INS-BOL-0008</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Universidad Provincial de Laguna Blanca</t>
+          <t>Universidad Nacional Siglo XX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Universidad Provincial de Laguna Blanca</t>
+          <t>Universidad Nacional Siglo XX</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Laguna Blanca</t>
+          <t>Llallagua</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -60879,7 +61011,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://www.argentina.gob.ar/educacion/universidades/informacion-universitaria/instituciones-universitarias</t>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -60896,17 +61028,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>INS-BOL-0008</t>
+          <t>INS-BOL-0011</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Universidad Nacional Siglo XX</t>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Universidad Nacional Siglo XX</t>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -60921,7 +61053,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Llallagua</t>
+          <t>Warisata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -60958,17 +61090,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INS-BOL-0011</t>
+          <t>INS-BOL-0013</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -60983,7 +61115,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warisata</t>
+          <t>Kuruyuki</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -61020,32 +61152,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INS-BOL-0013</t>
+          <t>INS-BRA-0133</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+          <t>Universidade do Grande Rio</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+          <t>Universidade do Grande Rio</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Kuruyuki</t>
+          <t>Duque de Caxias</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -61055,7 +61187,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Public</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -61065,7 +61197,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -61082,32 +61214,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>INS-BRA-0133</t>
+          <t>INS-PRY-0056</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Universidade do Grande Rio</t>
+          <t>Universidad Santa Clara de Asís</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Universidade do Grande Rio</t>
+          <t>Universidad Santa Clara de Asís</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Duque de Caxias</t>
+          <t>Caaguazú</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -61127,7 +61259,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+          <t>https://cones.gov.py/universidades/</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -61144,37 +61276,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>INS-PRY-0038</t>
+          <t>INS-VEN-0032</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Canindeyú</t>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Universidad Nacional de Canindeyú</t>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saltos del Guairá</t>
+          <t>Mantecal</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Technical University</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -61189,7 +61321,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://cones.gov.py/universidades/</t>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -61206,42 +61338,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INS-PRY-0056</t>
+          <t>INS-VEN-0043</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Universidad Santa Clara de Asís</t>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Universidad Santa Clara de Asís</t>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PRY</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Caaguazú</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>University</t>
+          <t>Agricultural University</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Public</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -61251,7 +61378,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://cones.gov.py/universidades/</t>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -61260,125 +61387,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>INS-VEN-0032</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Mantecal</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Technical University</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>INS-VEN-0043</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
         <is>
           <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
         </is>

--- a/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
+++ b/workspace/import-sources/universities/stage-1/South_America_Universities_Import_English_12_Countries_COMPLETE.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P875"/>
+  <dimension ref="A1:P882"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="84" min="1" max="1"/>
@@ -902,7 +902,6 @@
       <c r="K2" s="1" t="n"/>
       <c r="L2" s="1" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4" ht="32" customHeight="1" s="84">
       <c r="A4" s="26" t="inlineStr">
         <is>
@@ -59772,13 +59771,510 @@
         </is>
       </c>
     </row>
-    <row r="876" ht="28" customHeight="1" s="84"/>
-    <row r="877" ht="28" customHeight="1" s="84"/>
-    <row r="878" ht="28" customHeight="1" s="84"/>
-    <row r="879" ht="28" customHeight="1" s="84"/>
-    <row r="880" ht="28" customHeight="1" s="84"/>
-    <row r="881" ht="28" customHeight="1" s="84"/>
-    <row r="882" ht="28" customHeight="1" s="84"/>
+    <row r="876" ht="28" customHeight="1" s="84">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>INS-BOL-0008</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Siglo XX</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>Universidad Nacional Siglo XX</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>Llallagua</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>city_bo_official_llallagua</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>BO-P</t>
+        </is>
+      </c>
+      <c r="O876" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P876" t="inlineStr">
+        <is>
+          <t>USER_RESEARCH_ADDRESS_REQUIRES_OWNER_VERIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="877" ht="28" customHeight="1" s="84">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>INS-BOL-0011</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>Warisata</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>city_bo_official_warisata</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>BO-L</t>
+        </is>
+      </c>
+      <c r="O877" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P877" t="inlineStr">
+        <is>
+          <t>USER_RESEARCH_ADDRESS_REQUIRES_OWNER_VERIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="878" ht="28" customHeight="1" s="84">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>INS-BOL-0013</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Bolivia</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>BOL</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>Ivo</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>city_bo_official_ivo</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>BO-H</t>
+        </is>
+      </c>
+      <c r="O878" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P878" t="inlineStr">
+        <is>
+          <t>USER_RESEARCH_ADDRESS_REQUIRES_OWNER_VERIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="879" ht="28" customHeight="1" s="84">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>INS-BRA-0133</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Universidade do Grande Rio</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>Universidade do Grande Rio</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>BRA</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>Duque de Caxias</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>city_br_official_duque_de_caxias</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>BR-RJ</t>
+        </is>
+      </c>
+      <c r="O879" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P879" t="inlineStr">
+        <is>
+          <t>USER_RESEARCH_ADDRESS_REQUIRES_OWNER_VERIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="880" ht="28" customHeight="1" s="84">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>INS-PRY-0056</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Universidad Santa Clara de Asís</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>Universidad Santa Clara de Asís</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>PRY</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>Caaguazú</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>University</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>https://cones.gov.py/universidades/</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>city_py_official_caaguazu</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>PY-5</t>
+        </is>
+      </c>
+      <c r="O880" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P880" t="inlineStr">
+        <is>
+          <t>USER_RESEARCH_ADDRESS_REQUIRES_OWNER_VERIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="881" ht="28" customHeight="1" s="84">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>INS-VEN-0032</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>Mantecal</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>Technical University</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>city_ve_official_mantecal</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>VE-C</t>
+        </is>
+      </c>
+      <c r="O881" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P881" t="inlineStr">
+        <is>
+          <t>USER_RESEARCH_ADDRESS_REQUIRES_OWNER_VERIFICATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="882" ht="28" customHeight="1" s="84">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>INS-VEN-0043</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>Barquisimeto</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>Agricultural University</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>Public</t>
+        </is>
+      </c>
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>city_ve_barquisimeto</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>VE-K</t>
+        </is>
+      </c>
+      <c r="O882" t="inlineStr">
+        <is>
+          <t>SOURCE_MATCHED</t>
+        </is>
+      </c>
+      <c r="P882" t="inlineStr">
+        <is>
+          <t>USER_RESEARCH_ADDRESS_REQUIRES_OWNER_VERIFICATION</t>
+        </is>
+      </c>
+    </row>
     <row r="883" ht="28" customHeight="1" s="84"/>
   </sheetData>
   <mergeCells count="2">
@@ -60816,7 +61312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60959,436 +61455,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>INS-BOL-0008</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Siglo XX</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Universidad Nacional Siglo XX</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Llallagua</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INS-BOL-0011</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Universidad Indígena Boliviana Aymara Túpac Katari</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Warisata</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INS-BOL-0013</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Universidad Indígena Boliviana Guaraní y Pueblos de Tierras Bajas Apiaguaiki Tüpa</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bolivia</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>BOL</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Kuruyuki</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://ceub.edu.bo/universidades-del-sistema/ | https://dgesu.minedu.gob.bo/</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>INS-BRA-0133</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Universidade do Grande Rio</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Universidade do Grande Rio</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Brazil</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>BRA</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Duque de Caxias</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://emec.mec.gov.br/ | https://www.gov.br/mec/pt-br/politica-regulacao-supervisao-educacao-superior/cadastro-nacional-de-cursos-e-ies</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>INS-PRY-0056</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Universidad Santa Clara de Asís</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Universidad Santa Clara de Asís</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Paraguay</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>PRY</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Caaguazú</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>University</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://cones.gov.py/universidades/</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>INS-VEN-0032</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Universidad Politécnica Territorial del Alto Apure Pedro Camejo</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Mantecal</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Technical University</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>INS-VEN-0043</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Universidad Campesina de Venezuela Argimiro Gabaldón</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Agricultural University</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Public</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://cnu.gob.ve/wp-content/uploads/2024/04/Directorio-CNU-Abril-2024.pdf | https://loeu.opsu.gob.ve/ieu/</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>REVIEW_REQUIRED</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>OFFICIAL_ADDRESS_NOT_YET_CORROBORATED</t>
+          <t>USER_BATCH12_PARTIAL_EVIDENCE_REQUIRES_REVIEW</t>
         </is>
       </c>
     </row>
